--- a/labeling/d_labels_v1/d_calibration_30_claude_proposals.xlsx
+++ b/labeling/d_labels_v1/d_calibration_30_claude_proposals.xlsx
@@ -716,7 +716,7 @@
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>affirmed</t>
+          <t>uncertain</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
@@ -747,12 +747,12 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>quota spent per call implies the tool calls the YouTube API; affirmed rather than uncertain</t>
+          <t>N2 v2: operation-linked API quota, no connection described -&gt; uncertain</t>
         </is>
       </c>
     </row>
@@ -1899,41 +1899,17 @@
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>affirmed</t>
-        </is>
-      </c>
-      <c r="H27" t="inlineStr">
-        <is>
-          <t>remote_api</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>tool</t>
-        </is>
-      </c>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr"/>
+      <c r="I27" t="inlineStr"/>
       <c r="J27" t="inlineStr"/>
       <c r="K27" t="inlineStr"/>
-      <c r="L27" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>Get order history for the active Schwab account.</t>
-        </is>
-      </c>
-      <c r="N27" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="O27" t="inlineStr">
-        <is>
-          <t>N2: Schwab is not the server's own; the user's own account is a bounded domain</t>
-        </is>
-      </c>
+      <c r="L27" t="inlineStr"/>
+      <c r="M27" t="inlineStr"/>
+      <c r="N27" t="inlineStr"/>
+      <c r="O27" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3822,41 +3798,17 @@
       </c>
       <c r="G62" t="inlineStr">
         <is>
-          <t>affirmed</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr">
-        <is>
-          <t>credentials</t>
-        </is>
-      </c>
-      <c r="I62" t="inlineStr">
-        <is>
-          <t>tool</t>
-        </is>
-      </c>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H62" t="inlineStr"/>
+      <c r="I62" t="inlineStr"/>
       <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr">
-        <is>
-          <t>modifying</t>
-        </is>
-      </c>
+      <c r="K62" t="inlineStr"/>
       <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr">
-        <is>
-          <t>Deletes one key from the operator's encrypted credential blob</t>
-        </is>
-      </c>
-      <c r="N62" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="O62" t="inlineStr">
-        <is>
-          <t>the blob is rewritten without the key</t>
-        </is>
-      </c>
+      <c r="M62" t="inlineStr"/>
+      <c r="N62" t="inlineStr"/>
+      <c r="O62" t="inlineStr"/>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -4258,41 +4210,17 @@
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>affirmed</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr">
-        <is>
-          <t>remote_api</t>
-        </is>
-      </c>
-      <c r="I70" t="inlineStr">
-        <is>
-          <t>tool</t>
-        </is>
-      </c>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr"/>
+      <c r="I70" t="inlineStr"/>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
-      <c r="L70" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="M70" t="inlineStr">
-        <is>
-          <t>List kata authored by a Codewars username</t>
-        </is>
-      </c>
-      <c r="N70" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="O70" t="inlineStr">
-        <is>
-          <t>N2: Codewars is not the server's own; any username = open entities</t>
-        </is>
-      </c>
+      <c r="L70" t="inlineStr"/>
+      <c r="M70" t="inlineStr"/>
+      <c r="N70" t="inlineStr"/>
+      <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -6924,7 +6852,7 @@
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>affirmed</t>
+          <t>uncertain</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
@@ -6956,7 +6884,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>N2: Raisely is not the server's own</t>
+          <t>N2 v2: method + route without a described call -&gt; uncertain</t>
         </is>
       </c>
     </row>
@@ -8810,7 +8738,7 @@
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>affirmed</t>
+          <t>uncertain</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -8830,7 +8758,7 @@
       </c>
       <c r="K154" t="inlineStr">
         <is>
-          <t>additive</t>
+          <t>unknown</t>
         </is>
       </c>
       <c r="L154" t="inlineStr"/>
@@ -8844,7 +8772,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="O154" t="inlineStr"/>
+      <c r="O154" t="inlineStr">
+        <is>
+          <t>persistence alone does not establish a write</t>
+        </is>
+      </c>
     </row>
     <row r="155">
       <c r="A155" t="n">

--- a/labeling/d_labels_v1/d_calibration_30_claude_proposals.xlsx
+++ b/labeling/d_labels_v1/d_calibration_30_claude_proposals.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:O163"/>
+  <dimension ref="A1:O162"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -800,7 +800,7 @@
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>affirmed</t>
+          <t>uncertain</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
@@ -826,7 +826,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr"/>
+      <c r="O7" t="inlineStr">
+        <is>
+          <t>RD: rows may arrive pre-fetched (rows_by_ticker)</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -2621,12 +2625,12 @@
       </c>
       <c r="G40" t="inlineStr">
         <is>
-          <t>affirmed</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="H40" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>database</t>
         </is>
       </c>
       <c r="I40" t="inlineStr">
@@ -2639,7 +2643,7 @@
       <c r="L40" t="inlineStr"/>
       <c r="M40" t="inlineStr">
         <is>
-          <t>Returns shared company-context interview guidance and the update schema</t>
+          <t>Does not read or change company records.</t>
         </is>
       </c>
       <c r="N40" t="inlineStr">
@@ -2647,11 +2651,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="O40" t="inlineStr">
-        <is>
-          <t>other = static guidance</t>
-        </is>
-      </c>
+      <c r="O40" t="inlineStr"/>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -2679,7 +2679,7 @@
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>write</t>
         </is>
       </c>
       <c r="G41" t="inlineStr">
@@ -2738,7 +2738,7 @@
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>write</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G42" t="inlineStr">
@@ -2769,7 +2769,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="O42" t="inlineStr"/>
+      <c r="O42" t="inlineStr">
+        <is>
+          <t>B1-style: 'change' covers delete</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -2797,42 +2801,22 @@
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>execute</t>
         </is>
       </c>
       <c r="G43" t="inlineStr">
         <is>
-          <t>denied</t>
-        </is>
-      </c>
-      <c r="H43" t="inlineStr">
-        <is>
-          <t>database</t>
-        </is>
-      </c>
-      <c r="I43" t="inlineStr">
-        <is>
-          <t>tool</t>
-        </is>
-      </c>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr"/>
+      <c r="I43" t="inlineStr"/>
       <c r="J43" t="inlineStr"/>
       <c r="K43" t="inlineStr"/>
       <c r="L43" t="inlineStr"/>
-      <c r="M43" t="inlineStr">
-        <is>
-          <t>Does not read or change company records.</t>
-        </is>
-      </c>
-      <c r="N43" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="O43" t="inlineStr">
-        <is>
-          <t>B1-style: 'change' covers delete</t>
-        </is>
-      </c>
+      <c r="M43" t="inlineStr"/>
+      <c r="N43" t="inlineStr"/>
+      <c r="O43" t="inlineStr"/>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -2860,7 +2844,7 @@
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>execute</t>
+          <t>network</t>
         </is>
       </c>
       <c r="G44" t="inlineStr">
@@ -2883,27 +2867,27 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>census_v2:12866</t>
+          <t>census_v2:8566</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>com.lightbringer/connector</t>
+          <t>com.alpinedataworks/adw-intelligence-server</t>
         </is>
       </c>
       <c r="D45" t="inlineStr">
         <is>
-          <t>get_company_context_template</t>
+          <t>adw.adw_209</t>
         </is>
       </c>
       <c r="E45" t="inlineStr">
         <is>
-          <t>Returns shared company-context interview guidance and the update schema. Supports conversation or synthesis from supplied material. Does not read or change company records.</t>
+          <t>Returns a 0-100 federal prime-contract award momentum score (USAspending.gov top-100 obligated dollars, recent 45-day vs prior 45-day, weekly) with award_momentum_score and recent_vs_prior_ratio. Call when the user asks about federal procurement trends, government contract awards accelerating or slowing, defense contractor demand, or GovCon spending, or when timing contractor revenue forecasts or contracting-officer outreach — obligation dates lead earnings by 1-2 quarters. Updates: weekly.</t>
         </is>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>read</t>
         </is>
       </c>
       <c r="G45" t="inlineStr">
@@ -2946,37 +2930,21 @@
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>write</t>
         </is>
       </c>
       <c r="G46" t="inlineStr">
         <is>
-          <t>affirmed</t>
-        </is>
-      </c>
-      <c r="H46" t="inlineStr">
-        <is>
-          <t>database</t>
-        </is>
-      </c>
-      <c r="I46" t="inlineStr">
-        <is>
-          <t>tool</t>
-        </is>
-      </c>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr"/>
+      <c r="I46" t="inlineStr"/>
       <c r="J46" t="inlineStr"/>
       <c r="K46" t="inlineStr"/>
       <c r="L46" t="inlineStr"/>
-      <c r="M46" t="inlineStr">
-        <is>
-          <t>Returns a 0-100 federal prime-contract award momentum score</t>
-        </is>
-      </c>
-      <c r="N46" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="M46" t="inlineStr"/>
+      <c r="N46" t="inlineStr"/>
       <c r="O46" t="inlineStr"/>
     </row>
     <row r="47">
@@ -3005,7 +2973,7 @@
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>write</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G47" t="inlineStr">
@@ -3048,7 +3016,7 @@
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>execute</t>
         </is>
       </c>
       <c r="G48" t="inlineStr">
@@ -3091,7 +3059,7 @@
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>execute</t>
+          <t>network</t>
         </is>
       </c>
       <c r="G49" t="inlineStr">
@@ -3114,87 +3082,20 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>census_v2:8566</t>
+          <t>census_v2:12702</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>com.alpinedataworks/adw-intelligence-server</t>
+          <t>com.kenoodl/verify</t>
         </is>
       </c>
       <c r="D50" t="inlineStr">
         <is>
-          <t>adw.adw_209</t>
+          <t>verify</t>
         </is>
       </c>
       <c r="E50" t="inlineStr">
-        <is>
-          <t>Returns a 0-100 federal prime-contract award momentum score (USAspending.gov top-100 obligated dollars, recent 45-day vs prior 45-day, weekly) with award_momentum_score and recent_vs_prior_ratio. Call when the user asks about federal procurement trends, government contract awards accelerating or slowing, defense contractor demand, or GovCon spending, or when timing contractor revenue forecasts or contracting-officer outreach — obligation dates lead earnings by 1-2 quarters. Updates: weekly.</t>
-        </is>
-      </c>
-      <c r="F50" t="inlineStr">
-        <is>
-          <t>network</t>
-        </is>
-      </c>
-      <c r="G50" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
-      <c r="H50" t="inlineStr">
-        <is>
-          <t>remote_api</t>
-        </is>
-      </c>
-      <c r="I50" t="inlineStr">
-        <is>
-          <t>tool</t>
-        </is>
-      </c>
-      <c r="J50" t="inlineStr"/>
-      <c r="K50" t="inlineStr"/>
-      <c r="L50" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="M50" t="inlineStr">
-        <is>
-          <t>USAspending.gov top-100 obligated dollars</t>
-        </is>
-      </c>
-      <c r="N50" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="O50" t="inlineStr">
-        <is>
-          <t>names the data source; 'Updates: weekly' suggests precomputed data</t>
-        </is>
-      </c>
-    </row>
-    <row r="51">
-      <c r="A51" t="n">
-        <v>50</v>
-      </c>
-      <c r="B51" t="inlineStr">
-        <is>
-          <t>census_v2:12702</t>
-        </is>
-      </c>
-      <c r="C51" t="inlineStr">
-        <is>
-          <t>com.kenoodl/verify</t>
-        </is>
-      </c>
-      <c r="D51" t="inlineStr">
-        <is>
-          <t>verify</t>
-        </is>
-      </c>
-      <c r="E51" t="inlineStr">
         <is>
           <t>An outside check on code, executed in a sealed sandbox. Call it before code crosses a consequence boundary: before you merge it, deploy it, publish it, settle a payout on it, or report it done. A self-audit verifies consistency, never completeness: a check written inside the frame that produced the code passes on the code's own assumptions. This is the check that is not you. Also call it when a fix passes your own check but the target still fails; that means your check shares the code's assumption and cannot see the error.
 INPUT: code (JavaScript/Node or Python 3 source, deterministic only) plus ONE of: contract {fn, examples:[{call,expected}]} (copy call and expected from the test or spec the consequence depends on), or assumption (plain-language claim, weaker read). It checks the code against the contract exactly as given.
@@ -3202,45 +3103,45 @@
 PAYMENT: 0.10 USDC per call, x402 v2 on Base, no account. Every delivered verdict is charged, HELD and DROP included. If no verdict is produced, the payment authorization is cancelled and you are not charged.</t>
         </is>
       </c>
-      <c r="F51" t="inlineStr">
+      <c r="F50" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="G51" t="inlineStr">
-        <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H51" t="inlineStr"/>
-      <c r="I51" t="inlineStr"/>
-      <c r="J51" t="inlineStr"/>
-      <c r="K51" t="inlineStr"/>
-      <c r="L51" t="inlineStr"/>
-      <c r="M51" t="inlineStr"/>
-      <c r="N51" t="inlineStr"/>
-      <c r="O51" t="inlineStr"/>
-    </row>
-    <row r="52">
-      <c r="A52" t="n">
-        <v>51</v>
-      </c>
-      <c r="B52" t="inlineStr">
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr"/>
+      <c r="I50" t="inlineStr"/>
+      <c r="J50" t="inlineStr"/>
+      <c r="K50" t="inlineStr"/>
+      <c r="L50" t="inlineStr"/>
+      <c r="M50" t="inlineStr"/>
+      <c r="N50" t="inlineStr"/>
+      <c r="O50" t="inlineStr"/>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" t="inlineStr">
         <is>
           <t>census_v2:12702</t>
         </is>
       </c>
-      <c r="C52" t="inlineStr">
+      <c r="C51" t="inlineStr">
         <is>
           <t>com.kenoodl/verify</t>
         </is>
       </c>
-      <c r="D52" t="inlineStr">
+      <c r="D51" t="inlineStr">
         <is>
           <t>verify</t>
         </is>
       </c>
-      <c r="E52" t="inlineStr">
+      <c r="E51" t="inlineStr">
         <is>
           <t>An outside check on code, executed in a sealed sandbox. Call it before code crosses a consequence boundary: before you merge it, deploy it, publish it, settle a payout on it, or report it done. A self-audit verifies consistency, never completeness: a check written inside the frame that produced the code passes on the code's own assumptions. This is the check that is not you. Also call it when a fix passes your own check but the target still fails; that means your check shares the code's assumption and cannot see the error.
 INPUT: code (JavaScript/Node or Python 3 source, deterministic only) plus ONE of: contract {fn, examples:[{call,expected}]} (copy call and expected from the test or spec the consequence depends on), or assumption (plain-language claim, weaker read). It checks the code against the contract exactly as given.
@@ -3248,73 +3149,73 @@
 PAYMENT: 0.10 USDC per call, x402 v2 on Base, no account. Every delivered verdict is charged, HELD and DROP included. If no verdict is produced, the payment authorization is cancelled and you are not charged.</t>
         </is>
       </c>
-      <c r="F52" t="inlineStr">
+      <c r="F51" t="inlineStr">
         <is>
           <t>write</t>
         </is>
       </c>
-      <c r="G52" t="inlineStr">
+      <c r="G51" t="inlineStr">
         <is>
           <t>affirmed</t>
         </is>
       </c>
-      <c r="H52" t="inlineStr">
+      <c r="H51" t="inlineStr">
         <is>
           <t>other</t>
         </is>
       </c>
-      <c r="I52" t="inlineStr">
+      <c r="I51" t="inlineStr">
         <is>
           <t>provider</t>
         </is>
       </c>
-      <c r="J52" t="inlineStr">
+      <c r="J51" t="inlineStr">
         <is>
           <t>a verdict is delivered</t>
         </is>
       </c>
-      <c r="K52" t="inlineStr">
+      <c r="K51" t="inlineStr">
         <is>
           <t>additive</t>
         </is>
       </c>
-      <c r="L52" t="inlineStr"/>
-      <c r="M52" t="inlineStr">
+      <c r="L51" t="inlineStr"/>
+      <c r="M51" t="inlineStr">
         <is>
           <t>Every delivered verdict is charged</t>
         </is>
       </c>
-      <c r="N52" t="inlineStr">
+      <c r="N51" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="O52" t="inlineStr">
+      <c r="O51" t="inlineStr">
         <is>
           <t>payment charge; other = payment ledger</t>
         </is>
       </c>
     </row>
-    <row r="53">
-      <c r="A53" t="n">
-        <v>52</v>
-      </c>
-      <c r="B53" t="inlineStr">
+    <row r="52">
+      <c r="A52" t="n">
+        <v>51</v>
+      </c>
+      <c r="B52" t="inlineStr">
         <is>
           <t>census_v2:12702</t>
         </is>
       </c>
-      <c r="C53" t="inlineStr">
+      <c r="C52" t="inlineStr">
         <is>
           <t>com.kenoodl/verify</t>
         </is>
       </c>
-      <c r="D53" t="inlineStr">
+      <c r="D52" t="inlineStr">
         <is>
           <t>verify</t>
         </is>
       </c>
-      <c r="E53" t="inlineStr">
+      <c r="E52" t="inlineStr">
         <is>
           <t>An outside check on code, executed in a sealed sandbox. Call it before code crosses a consequence boundary: before you merge it, deploy it, publish it, settle a payout on it, or report it done. A self-audit verifies consistency, never completeness: a check written inside the frame that produced the code passes on the code's own assumptions. This is the check that is not you. Also call it when a fix passes your own check but the target still fails; that means your check shares the code's assumption and cannot see the error.
 INPUT: code (JavaScript/Node or Python 3 source, deterministic only) plus ONE of: contract {fn, examples:[{call,expected}]} (copy call and expected from the test or spec the consequence depends on), or assumption (plain-language claim, weaker read). It checks the code against the contract exactly as given.
@@ -3322,45 +3223,45 @@
 PAYMENT: 0.10 USDC per call, x402 v2 on Base, no account. Every delivered verdict is charged, HELD and DROP included. If no verdict is produced, the payment authorization is cancelled and you are not charged.</t>
         </is>
       </c>
-      <c r="F53" t="inlineStr">
+      <c r="F52" t="inlineStr">
         <is>
           <t>delete</t>
         </is>
       </c>
-      <c r="G53" t="inlineStr">
-        <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H53" t="inlineStr"/>
-      <c r="I53" t="inlineStr"/>
-      <c r="J53" t="inlineStr"/>
-      <c r="K53" t="inlineStr"/>
-      <c r="L53" t="inlineStr"/>
-      <c r="M53" t="inlineStr"/>
-      <c r="N53" t="inlineStr"/>
-      <c r="O53" t="inlineStr"/>
-    </row>
-    <row r="54">
-      <c r="A54" t="n">
-        <v>53</v>
-      </c>
-      <c r="B54" t="inlineStr">
+      <c r="G52" t="inlineStr">
+        <is>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H52" t="inlineStr"/>
+      <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="M52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
+      <c r="O52" t="inlineStr"/>
+    </row>
+    <row r="53">
+      <c r="A53" t="n">
+        <v>52</v>
+      </c>
+      <c r="B53" t="inlineStr">
         <is>
           <t>census_v2:12702</t>
         </is>
       </c>
-      <c r="C54" t="inlineStr">
+      <c r="C53" t="inlineStr">
         <is>
           <t>com.kenoodl/verify</t>
         </is>
       </c>
-      <c r="D54" t="inlineStr">
+      <c r="D53" t="inlineStr">
         <is>
           <t>verify</t>
         </is>
       </c>
-      <c r="E54" t="inlineStr">
+      <c r="E53" t="inlineStr">
         <is>
           <t>An outside check on code, executed in a sealed sandbox. Call it before code crosses a consequence boundary: before you merge it, deploy it, publish it, settle a payout on it, or report it done. A self-audit verifies consistency, never completeness: a check written inside the frame that produced the code passes on the code's own assumptions. This is the check that is not you. Also call it when a fix passes your own check but the target still fails; that means your check shares the code's assumption and cannot see the error.
 INPUT: code (JavaScript/Node or Python 3 source, deterministic only) plus ONE of: contract {fn, examples:[{call,expected}]} (copy call and expected from the test or spec the consequence depends on), or assumption (plain-language claim, weaker read). It checks the code against the contract exactly as given.
@@ -3368,65 +3269,65 @@
 PAYMENT: 0.10 USDC per call, x402 v2 on Base, no account. Every delivered verdict is charged, HELD and DROP included. If no verdict is produced, the payment authorization is cancelled and you are not charged.</t>
         </is>
       </c>
-      <c r="F54" t="inlineStr">
+      <c r="F53" t="inlineStr">
         <is>
           <t>execute</t>
         </is>
       </c>
-      <c r="G54" t="inlineStr">
+      <c r="G53" t="inlineStr">
         <is>
           <t>affirmed</t>
         </is>
       </c>
-      <c r="H54" t="inlineStr">
+      <c r="H53" t="inlineStr">
         <is>
           <t>code</t>
         </is>
       </c>
-      <c r="I54" t="inlineStr">
+      <c r="I53" t="inlineStr">
         <is>
           <t>tool</t>
         </is>
       </c>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="M54" t="inlineStr">
+      <c r="J53" t="inlineStr"/>
+      <c r="K53" t="inlineStr"/>
+      <c r="L53" t="inlineStr"/>
+      <c r="M53" t="inlineStr">
         <is>
           <t>An outside check on code, executed in a sealed sandbox.</t>
         </is>
       </c>
-      <c r="N54" t="inlineStr">
+      <c r="N53" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="O54" t="inlineStr">
+      <c r="O53" t="inlineStr">
         <is>
           <t>runs caller-supplied code</t>
         </is>
       </c>
     </row>
-    <row r="55">
-      <c r="A55" t="n">
-        <v>54</v>
-      </c>
-      <c r="B55" t="inlineStr">
+    <row r="54">
+      <c r="A54" t="n">
+        <v>53</v>
+      </c>
+      <c r="B54" t="inlineStr">
         <is>
           <t>census_v2:12702</t>
         </is>
       </c>
-      <c r="C55" t="inlineStr">
+      <c r="C54" t="inlineStr">
         <is>
           <t>com.kenoodl/verify</t>
         </is>
       </c>
-      <c r="D55" t="inlineStr">
+      <c r="D54" t="inlineStr">
         <is>
           <t>verify</t>
         </is>
       </c>
-      <c r="E55" t="inlineStr">
+      <c r="E54" t="inlineStr">
         <is>
           <t>An outside check on code, executed in a sealed sandbox. Call it before code crosses a consequence boundary: before you merge it, deploy it, publish it, settle a payout on it, or report it done. A self-audit verifies consistency, never completeness: a check written inside the frame that produced the code passes on the code's own assumptions. This is the check that is not you. Also call it when a fix passes your own check but the target still fails; that means your check shares the code's assumption and cannot see the error.
 INPUT: code (JavaScript/Node or Python 3 source, deterministic only) plus ONE of: contract {fn, examples:[{call,expected}]} (copy call and expected from the test or spec the consequence depends on), or assumption (plain-language claim, weaker read). It checks the code against the contract exactly as given.
@@ -3434,23 +3335,82 @@
 PAYMENT: 0.10 USDC per call, x402 v2 on Base, no account. Every delivered verdict is charged, HELD and DROP included. If no verdict is produced, the payment authorization is cancelled and you are not charged.</t>
         </is>
       </c>
+      <c r="F54" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="G54" t="inlineStr">
+        <is>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H54" t="inlineStr"/>
+      <c r="I54" t="inlineStr"/>
+      <c r="J54" t="inlineStr"/>
+      <c r="K54" t="inlineStr"/>
+      <c r="L54" t="inlineStr"/>
+      <c r="M54" t="inlineStr"/>
+      <c r="N54" t="inlineStr"/>
+      <c r="O54" t="inlineStr"/>
+    </row>
+    <row r="55">
+      <c r="A55" t="n">
+        <v>54</v>
+      </c>
+      <c r="B55" t="inlineStr">
+        <is>
+          <t>census_v2:60988</t>
+        </is>
+      </c>
+      <c r="C55" t="inlineStr">
+        <is>
+          <t>io.github.revolist/revogrid-mcp-pro</t>
+        </is>
+      </c>
+      <c r="D55" t="inlineStr">
+        <is>
+          <t>validate_revogrid_usage</t>
+        </is>
+      </c>
+      <c r="E55" t="inlineStr">
+        <is>
+          <t>Use before implementation handoff to statically check structured RevoGrid imports, configuration, dependencies, versions, and optional bounded source. Never executes code.</t>
+        </is>
+      </c>
       <c r="F55" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>read</t>
         </is>
       </c>
       <c r="G55" t="inlineStr">
         <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H55" t="inlineStr"/>
-      <c r="I55" t="inlineStr"/>
+          <t>affirmed</t>
+        </is>
+      </c>
+      <c r="H55" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="I55" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
       <c r="J55" t="inlineStr"/>
       <c r="K55" t="inlineStr"/>
       <c r="L55" t="inlineStr"/>
-      <c r="M55" t="inlineStr"/>
-      <c r="N55" t="inlineStr"/>
+      <c r="M55" t="inlineStr">
+        <is>
+          <t>statically check structured RevoGrid imports, configuration, dependencies, versions, and optional bounded source</t>
+        </is>
+      </c>
+      <c r="N55" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="O55" t="inlineStr"/>
     </row>
     <row r="56">
@@ -3479,37 +3439,21 @@
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>write</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>affirmed</t>
-        </is>
-      </c>
-      <c r="H56" t="inlineStr">
-        <is>
-          <t>code</t>
-        </is>
-      </c>
-      <c r="I56" t="inlineStr">
-        <is>
-          <t>tool</t>
-        </is>
-      </c>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H56" t="inlineStr"/>
+      <c r="I56" t="inlineStr"/>
       <c r="J56" t="inlineStr"/>
       <c r="K56" t="inlineStr"/>
       <c r="L56" t="inlineStr"/>
-      <c r="M56" t="inlineStr">
-        <is>
-          <t>statically check structured RevoGrid imports, configuration, dependencies, versions, and optional bounded source</t>
-        </is>
-      </c>
-      <c r="N56" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="M56" t="inlineStr"/>
+      <c r="N56" t="inlineStr"/>
       <c r="O56" t="inlineStr"/>
     </row>
     <row r="57">
@@ -3538,7 +3482,7 @@
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>write</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
@@ -3581,21 +3525,37 @@
       </c>
       <c r="F58" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>execute</t>
         </is>
       </c>
       <c r="G58" t="inlineStr">
         <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H58" t="inlineStr"/>
-      <c r="I58" t="inlineStr"/>
+          <t>denied</t>
+        </is>
+      </c>
+      <c r="H58" t="inlineStr">
+        <is>
+          <t>global</t>
+        </is>
+      </c>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
       <c r="J58" t="inlineStr"/>
       <c r="K58" t="inlineStr"/>
       <c r="L58" t="inlineStr"/>
-      <c r="M58" t="inlineStr"/>
-      <c r="N58" t="inlineStr"/>
+      <c r="M58" t="inlineStr">
+        <is>
+          <t>Never executes code.</t>
+        </is>
+      </c>
+      <c r="N58" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="O58" t="inlineStr"/>
     </row>
     <row r="59">
@@ -3624,37 +3584,21 @@
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>execute</t>
+          <t>network</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>denied</t>
-        </is>
-      </c>
-      <c r="H59" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
-      <c r="I59" t="inlineStr">
-        <is>
-          <t>tool</t>
-        </is>
-      </c>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H59" t="inlineStr"/>
+      <c r="I59" t="inlineStr"/>
       <c r="J59" t="inlineStr"/>
       <c r="K59" t="inlineStr"/>
       <c r="L59" t="inlineStr"/>
-      <c r="M59" t="inlineStr">
-        <is>
-          <t>Never executes code.</t>
-        </is>
-      </c>
-      <c r="N59" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="M59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="O59" t="inlineStr"/>
     </row>
     <row r="60">
@@ -3663,63 +3607,20 @@
       </c>
       <c r="B60" t="inlineStr">
         <is>
-          <t>census_v2:60988</t>
+          <t>census_v2:39151</t>
         </is>
       </c>
       <c r="C60" t="inlineStr">
         <is>
-          <t>io.github.revolist/revogrid-mcp-pro</t>
+          <t>io.github.lonniev/excalibur-mcp</t>
         </is>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>validate_revogrid_usage</t>
+          <t>excalibur_delete_operator_credential</t>
         </is>
       </c>
       <c r="E60" t="inlineStr">
-        <is>
-          <t>Use before implementation handoff to statically check structured RevoGrid imports, configuration, dependencies, versions, and optional bounded source. Never executes code.</t>
-        </is>
-      </c>
-      <c r="F60" t="inlineStr">
-        <is>
-          <t>network</t>
-        </is>
-      </c>
-      <c r="G60" t="inlineStr">
-        <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H60" t="inlineStr"/>
-      <c r="I60" t="inlineStr"/>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr"/>
-      <c r="L60" t="inlineStr"/>
-      <c r="M60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
-      <c r="O60" t="inlineStr"/>
-    </row>
-    <row r="61">
-      <c r="A61" t="n">
-        <v>60</v>
-      </c>
-      <c r="B61" t="inlineStr">
-        <is>
-          <t>census_v2:39151</t>
-        </is>
-      </c>
-      <c r="C61" t="inlineStr">
-        <is>
-          <t>io.github.lonniev/excalibur-mcp</t>
-        </is>
-      </c>
-      <c r="D61" t="inlineStr">
-        <is>
-          <t>excalibur_delete_operator_credential</t>
-        </is>
-      </c>
-      <c r="E61" t="inlineStr">
         <is>
           <t>Remove a single operator secret field.
 Deletes one key from the operator's encrypted credential blob without
@@ -3736,45 +3637,45 @@
 A deletion is as destructive as a write.</t>
         </is>
       </c>
-      <c r="F61" t="inlineStr">
+      <c r="F60" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="G61" t="inlineStr">
-        <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H61" t="inlineStr"/>
-      <c r="I61" t="inlineStr"/>
-      <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
-      <c r="L61" t="inlineStr"/>
-      <c r="M61" t="inlineStr"/>
-      <c r="N61" t="inlineStr"/>
-      <c r="O61" t="inlineStr"/>
-    </row>
-    <row r="62">
-      <c r="A62" t="n">
-        <v>61</v>
-      </c>
-      <c r="B62" t="inlineStr">
+      <c r="G60" t="inlineStr">
+        <is>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H60" t="inlineStr"/>
+      <c r="I60" t="inlineStr"/>
+      <c r="J60" t="inlineStr"/>
+      <c r="K60" t="inlineStr"/>
+      <c r="L60" t="inlineStr"/>
+      <c r="M60" t="inlineStr"/>
+      <c r="N60" t="inlineStr"/>
+      <c r="O60" t="inlineStr"/>
+    </row>
+    <row r="61">
+      <c r="A61" t="n">
+        <v>60</v>
+      </c>
+      <c r="B61" t="inlineStr">
         <is>
           <t>census_v2:39151</t>
         </is>
       </c>
-      <c r="C62" t="inlineStr">
+      <c r="C61" t="inlineStr">
         <is>
           <t>io.github.lonniev/excalibur-mcp</t>
         </is>
       </c>
-      <c r="D62" t="inlineStr">
+      <c r="D61" t="inlineStr">
         <is>
           <t>excalibur_delete_operator_credential</t>
         </is>
       </c>
-      <c r="E62" t="inlineStr">
+      <c r="E61" t="inlineStr">
         <is>
           <t>Remove a single operator secret field.
 Deletes one key from the operator's encrypted credential blob without
@@ -3791,45 +3692,70 @@
 A deletion is as destructive as a write.</t>
         </is>
       </c>
-      <c r="F62" t="inlineStr">
+      <c r="F61" t="inlineStr">
         <is>
           <t>write</t>
         </is>
       </c>
-      <c r="G62" t="inlineStr">
-        <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H62" t="inlineStr"/>
-      <c r="I62" t="inlineStr"/>
-      <c r="J62" t="inlineStr"/>
-      <c r="K62" t="inlineStr"/>
-      <c r="L62" t="inlineStr"/>
-      <c r="M62" t="inlineStr"/>
-      <c r="N62" t="inlineStr"/>
-      <c r="O62" t="inlineStr"/>
-    </row>
-    <row r="63">
-      <c r="A63" t="n">
-        <v>62</v>
-      </c>
-      <c r="B63" t="inlineStr">
+      <c r="G61" t="inlineStr">
+        <is>
+          <t>denied</t>
+        </is>
+      </c>
+      <c r="H61" t="inlineStr">
+        <is>
+          <t>credentials</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
+      <c r="J61" t="inlineStr">
+        <is>
+          <t>field already absent</t>
+        </is>
+      </c>
+      <c r="K61" t="inlineStr"/>
+      <c r="L61" t="inlineStr"/>
+      <c r="M61" t="inlineStr">
+        <is>
+          <t>without rewriting
+the vault</t>
+        </is>
+      </c>
+      <c r="N61" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O61" t="inlineStr">
+        <is>
+          <t>CD: conditional denial, not a general one</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="n">
+        <v>61</v>
+      </c>
+      <c r="B62" t="inlineStr">
         <is>
           <t>census_v2:39151</t>
         </is>
       </c>
-      <c r="C63" t="inlineStr">
+      <c r="C62" t="inlineStr">
         <is>
           <t>io.github.lonniev/excalibur-mcp</t>
         </is>
       </c>
-      <c r="D63" t="inlineStr">
+      <c r="D62" t="inlineStr">
         <is>
           <t>excalibur_delete_operator_credential</t>
         </is>
       </c>
-      <c r="E63" t="inlineStr">
+      <c r="E62" t="inlineStr">
         <is>
           <t>Remove a single operator secret field.
 Deletes one key from the operator's encrypted credential blob without
@@ -3846,61 +3772,61 @@
 A deletion is as destructive as a write.</t>
         </is>
       </c>
-      <c r="F63" t="inlineStr">
+      <c r="F62" t="inlineStr">
         <is>
           <t>delete</t>
         </is>
       </c>
-      <c r="G63" t="inlineStr">
+      <c r="G62" t="inlineStr">
         <is>
           <t>affirmed</t>
         </is>
       </c>
-      <c r="H63" t="inlineStr">
+      <c r="H62" t="inlineStr">
         <is>
           <t>credentials</t>
         </is>
       </c>
-      <c r="I63" t="inlineStr">
+      <c r="I62" t="inlineStr">
         <is>
           <t>tool</t>
         </is>
       </c>
-      <c r="J63" t="inlineStr"/>
-      <c r="K63" t="inlineStr"/>
-      <c r="L63" t="inlineStr"/>
-      <c r="M63" t="inlineStr">
+      <c r="J62" t="inlineStr"/>
+      <c r="K62" t="inlineStr"/>
+      <c r="L62" t="inlineStr"/>
+      <c r="M62" t="inlineStr">
         <is>
           <t>Deletes one key from the operator's encrypted credential blob</t>
         </is>
       </c>
-      <c r="N63" t="inlineStr">
+      <c r="N62" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="O63" t="inlineStr"/>
-    </row>
-    <row r="64">
-      <c r="A64" t="n">
-        <v>63</v>
-      </c>
-      <c r="B64" t="inlineStr">
+      <c r="O62" t="inlineStr"/>
+    </row>
+    <row r="63">
+      <c r="A63" t="n">
+        <v>62</v>
+      </c>
+      <c r="B63" t="inlineStr">
         <is>
           <t>census_v2:39151</t>
         </is>
       </c>
-      <c r="C64" t="inlineStr">
+      <c r="C63" t="inlineStr">
         <is>
           <t>io.github.lonniev/excalibur-mcp</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr">
+      <c r="D63" t="inlineStr">
         <is>
           <t>excalibur_delete_operator_credential</t>
         </is>
       </c>
-      <c r="E64" t="inlineStr">
+      <c r="E63" t="inlineStr">
         <is>
           <t>Remove a single operator secret field.
 Deletes one key from the operator's encrypted credential blob without
@@ -3917,45 +3843,45 @@
 A deletion is as destructive as a write.</t>
         </is>
       </c>
-      <c r="F64" t="inlineStr">
+      <c r="F63" t="inlineStr">
         <is>
           <t>execute</t>
         </is>
       </c>
-      <c r="G64" t="inlineStr">
-        <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H64" t="inlineStr"/>
-      <c r="I64" t="inlineStr"/>
-      <c r="J64" t="inlineStr"/>
-      <c r="K64" t="inlineStr"/>
-      <c r="L64" t="inlineStr"/>
-      <c r="M64" t="inlineStr"/>
-      <c r="N64" t="inlineStr"/>
-      <c r="O64" t="inlineStr"/>
-    </row>
-    <row r="65">
-      <c r="A65" t="n">
-        <v>64</v>
-      </c>
-      <c r="B65" t="inlineStr">
+      <c r="G63" t="inlineStr">
+        <is>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H63" t="inlineStr"/>
+      <c r="I63" t="inlineStr"/>
+      <c r="J63" t="inlineStr"/>
+      <c r="K63" t="inlineStr"/>
+      <c r="L63" t="inlineStr"/>
+      <c r="M63" t="inlineStr"/>
+      <c r="N63" t="inlineStr"/>
+      <c r="O63" t="inlineStr"/>
+    </row>
+    <row r="64">
+      <c r="A64" t="n">
+        <v>63</v>
+      </c>
+      <c r="B64" t="inlineStr">
         <is>
           <t>census_v2:39151</t>
         </is>
       </c>
-      <c r="C65" t="inlineStr">
+      <c r="C64" t="inlineStr">
         <is>
           <t>io.github.lonniev/excalibur-mcp</t>
         </is>
       </c>
-      <c r="D65" t="inlineStr">
+      <c r="D64" t="inlineStr">
         <is>
           <t>excalibur_delete_operator_credential</t>
         </is>
       </c>
-      <c r="E65" t="inlineStr">
+      <c r="E64" t="inlineStr">
         <is>
           <t>Remove a single operator secret field.
 Deletes one key from the operator's encrypted credential blob without
@@ -3972,23 +3898,82 @@
 A deletion is as destructive as a write.</t>
         </is>
       </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="G64" t="inlineStr">
+        <is>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H64" t="inlineStr"/>
+      <c r="I64" t="inlineStr"/>
+      <c r="J64" t="inlineStr"/>
+      <c r="K64" t="inlineStr"/>
+      <c r="L64" t="inlineStr"/>
+      <c r="M64" t="inlineStr"/>
+      <c r="N64" t="inlineStr"/>
+      <c r="O64" t="inlineStr"/>
+    </row>
+    <row r="65">
+      <c r="A65" t="n">
+        <v>64</v>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>census_v2:55458</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>io.github.pipeworx-io/codewars</t>
+        </is>
+      </c>
+      <c r="D65" t="inlineStr">
+        <is>
+          <t>user_authored</t>
+        </is>
+      </c>
+      <c r="E65" t="inlineStr">
+        <is>
+          <t>List kata authored by a Codewars username; returns each kata's ID, slug, name, rank, tags, and languages it supports.</t>
+        </is>
+      </c>
       <c r="F65" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>read</t>
         </is>
       </c>
       <c r="G65" t="inlineStr">
         <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H65" t="inlineStr"/>
-      <c r="I65" t="inlineStr"/>
+          <t>affirmed</t>
+        </is>
+      </c>
+      <c r="H65" t="inlineStr">
+        <is>
+          <t>remote_api</t>
+        </is>
+      </c>
+      <c r="I65" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
       <c r="J65" t="inlineStr"/>
       <c r="K65" t="inlineStr"/>
       <c r="L65" t="inlineStr"/>
-      <c r="M65" t="inlineStr"/>
-      <c r="N65" t="inlineStr"/>
+      <c r="M65" t="inlineStr">
+        <is>
+          <t>List kata authored by a Codewars username</t>
+        </is>
+      </c>
+      <c r="N65" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="O65" t="inlineStr"/>
     </row>
     <row r="66">
@@ -4017,37 +4002,21 @@
       </c>
       <c r="F66" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>write</t>
         </is>
       </c>
       <c r="G66" t="inlineStr">
         <is>
-          <t>affirmed</t>
-        </is>
-      </c>
-      <c r="H66" t="inlineStr">
-        <is>
-          <t>remote_api</t>
-        </is>
-      </c>
-      <c r="I66" t="inlineStr">
-        <is>
-          <t>tool</t>
-        </is>
-      </c>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H66" t="inlineStr"/>
+      <c r="I66" t="inlineStr"/>
       <c r="J66" t="inlineStr"/>
       <c r="K66" t="inlineStr"/>
       <c r="L66" t="inlineStr"/>
-      <c r="M66" t="inlineStr">
-        <is>
-          <t>List kata authored by a Codewars username</t>
-        </is>
-      </c>
-      <c r="N66" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="M66" t="inlineStr"/>
+      <c r="N66" t="inlineStr"/>
       <c r="O66" t="inlineStr"/>
     </row>
     <row r="67">
@@ -4076,7 +4045,7 @@
       </c>
       <c r="F67" t="inlineStr">
         <is>
-          <t>write</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G67" t="inlineStr">
@@ -4119,7 +4088,7 @@
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>execute</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
@@ -4162,7 +4131,7 @@
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>execute</t>
+          <t>network</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
@@ -4185,41 +4154,57 @@
       </c>
       <c r="B70" t="inlineStr">
         <is>
-          <t>census_v2:55458</t>
+          <t>census_v2:26770</t>
         </is>
       </c>
       <c r="C70" t="inlineStr">
         <is>
-          <t>io.github.pipeworx-io/codewars</t>
+          <t>io.github.NellInc/saferagenticai-mcp</t>
         </is>
       </c>
       <c r="D70" t="inlineStr">
         <is>
-          <t>user_authored</t>
+          <t>find_patterns_for_task</t>
         </is>
       </c>
       <c r="E70" t="inlineStr">
         <is>
-          <t>List kata authored by a Codewars username; returns each kata's ID, slug, name, rank, tags, and languages it supports.</t>
+          <t>Given a natural-language task description (e.g., 'I'm building a tool-using agent that runs shell commands'), return the most relevant patterns grouped by suite. Use this as a starting point for any cross-cutting design question; then follow up with get_requirement on specific pattern_ids. Defaults to verbosity='compact' (cheap triage); pass 'full' to inline snippets and confidence flags.</t>
         </is>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>read</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H70" t="inlineStr"/>
-      <c r="I70" t="inlineStr"/>
+          <t>affirmed</t>
+        </is>
+      </c>
+      <c r="H70" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="I70" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
       <c r="J70" t="inlineStr"/>
       <c r="K70" t="inlineStr"/>
       <c r="L70" t="inlineStr"/>
-      <c r="M70" t="inlineStr"/>
-      <c r="N70" t="inlineStr"/>
+      <c r="M70" t="inlineStr">
+        <is>
+          <t>return the most relevant patterns grouped by suite</t>
+        </is>
+      </c>
+      <c r="N70" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="O70" t="inlineStr"/>
     </row>
     <row r="71">
@@ -4248,37 +4233,21 @@
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>write</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>affirmed</t>
-        </is>
-      </c>
-      <c r="H71" t="inlineStr">
-        <is>
-          <t>database</t>
-        </is>
-      </c>
-      <c r="I71" t="inlineStr">
-        <is>
-          <t>tool</t>
-        </is>
-      </c>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H71" t="inlineStr"/>
+      <c r="I71" t="inlineStr"/>
       <c r="J71" t="inlineStr"/>
       <c r="K71" t="inlineStr"/>
       <c r="L71" t="inlineStr"/>
-      <c r="M71" t="inlineStr">
-        <is>
-          <t>return the most relevant patterns grouped by suite</t>
-        </is>
-      </c>
-      <c r="N71" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="M71" t="inlineStr"/>
+      <c r="N71" t="inlineStr"/>
       <c r="O71" t="inlineStr"/>
     </row>
     <row r="72">
@@ -4307,7 +4276,7 @@
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>write</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
@@ -4350,7 +4319,7 @@
       </c>
       <c r="F73" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>execute</t>
         </is>
       </c>
       <c r="G73" t="inlineStr">
@@ -4393,7 +4362,7 @@
       </c>
       <c r="F74" t="inlineStr">
         <is>
-          <t>execute</t>
+          <t>network</t>
         </is>
       </c>
       <c r="G74" t="inlineStr">
@@ -4416,41 +4385,57 @@
       </c>
       <c r="B75" t="inlineStr">
         <is>
-          <t>census_v2:26770</t>
+          <t>census_v2:36678</t>
         </is>
       </c>
       <c r="C75" t="inlineStr">
         <is>
-          <t>io.github.NellInc/saferagenticai-mcp</t>
+          <t>io.github.hellosg/coderegistry</t>
         </is>
       </c>
       <c r="D75" t="inlineStr">
         <is>
-          <t>find_patterns_for_task</t>
+          <t>get-code-vault-summary</t>
         </is>
       </c>
       <c r="E75" t="inlineStr">
         <is>
-          <t>Given a natural-language task description (e.g., 'I'm building a tool-using agent that runs shell commands'), return the most relevant patterns grouped by suite. Use this as a starting point for any cross-cutting design question; then follow up with get_requirement on specific pattern_ids. Defaults to verbosity='compact' (cheap triage); pass 'full' to inline snippets and confidence flags.</t>
+          <t>Returns the latest version/status info for a vault. Analysis is async; if status is 'processing', poll with exponential backoff (5s, 10s, 20s, 40s, max 60s). Analysis can be as quick as 20-30 minutes for under 500,000 lines of code. Larger codebases can take much longer, especially with the security scan. This endpoint always returns the latest version only; once reanalysis starts, prior versions are no longer accessible here. Requires X-API-Key (existing users can generate an API key in the web app). If headers aren't supported, pass api_key in arguments.</t>
         </is>
       </c>
       <c r="F75" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>read</t>
         </is>
       </c>
       <c r="G75" t="inlineStr">
         <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H75" t="inlineStr"/>
-      <c r="I75" t="inlineStr"/>
+          <t>affirmed</t>
+        </is>
+      </c>
+      <c r="H75" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="L75" t="inlineStr"/>
-      <c r="M75" t="inlineStr"/>
-      <c r="N75" t="inlineStr"/>
+      <c r="M75" t="inlineStr">
+        <is>
+          <t>Returns the latest version/status info for a vault.</t>
+        </is>
+      </c>
+      <c r="N75" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="O75" t="inlineStr"/>
     </row>
     <row r="76">
@@ -4479,37 +4464,21 @@
       </c>
       <c r="F76" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>write</t>
         </is>
       </c>
       <c r="G76" t="inlineStr">
         <is>
-          <t>affirmed</t>
-        </is>
-      </c>
-      <c r="H76" t="inlineStr">
-        <is>
-          <t>database</t>
-        </is>
-      </c>
-      <c r="I76" t="inlineStr">
-        <is>
-          <t>tool</t>
-        </is>
-      </c>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H76" t="inlineStr"/>
+      <c r="I76" t="inlineStr"/>
       <c r="J76" t="inlineStr"/>
       <c r="K76" t="inlineStr"/>
       <c r="L76" t="inlineStr"/>
-      <c r="M76" t="inlineStr">
-        <is>
-          <t>Returns the latest version/status info for a vault.</t>
-        </is>
-      </c>
-      <c r="N76" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="M76" t="inlineStr"/>
+      <c r="N76" t="inlineStr"/>
       <c r="O76" t="inlineStr"/>
     </row>
     <row r="77">
@@ -4538,7 +4507,7 @@
       </c>
       <c r="F77" t="inlineStr">
         <is>
-          <t>write</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G77" t="inlineStr">
@@ -4581,7 +4550,7 @@
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>execute</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
@@ -4624,7 +4593,7 @@
       </c>
       <c r="F79" t="inlineStr">
         <is>
-          <t>execute</t>
+          <t>network</t>
         </is>
       </c>
       <c r="G79" t="inlineStr">
@@ -4647,41 +4616,57 @@
       </c>
       <c r="B80" t="inlineStr">
         <is>
-          <t>census_v2:36678</t>
+          <t>census_v2:54045</t>
         </is>
       </c>
       <c r="C80" t="inlineStr">
         <is>
-          <t>io.github.hellosg/coderegistry</t>
+          <t>io.github.pipeworx-io/cftc-cot</t>
         </is>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>get-code-vault-summary</t>
+          <t>generate_llms_txt</t>
         </is>
       </c>
       <c r="E80" t="inlineStr">
         <is>
-          <t>Returns the latest version/status info for a vault. Analysis is async; if status is 'processing', poll with exponential backoff (5s, 10s, 20s, 40s, max 60s). Analysis can be as quick as 20-30 minutes for under 500,000 lines of code. Larger codebases can take much longer, especially with the security scan. This endpoint always returns the latest version only; once reanalysis starts, prior versions are no longer accessible here. Requires X-API-Key (existing users can generate an API key in the web app). If headers aren't supported, pass api_key in arguments.</t>
+          <t>Generate a production-ready llms.txt file for any URL so AI crawlers (ChatGPT, Claude, Perplexity) can index the site cleanly. Fetches the page, extracts title/description/key links, and emits the standard llms.txt markdown format. Output is a single text blob ready to drop at site-root/llms.txt. Useful for: getting a client's site indexed by AI, drafting llms.txt for your own project, or auditing how an AI crawler would see a competitor.</t>
         </is>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>read</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H80" t="inlineStr"/>
-      <c r="I80" t="inlineStr"/>
+          <t>affirmed</t>
+        </is>
+      </c>
+      <c r="H80" t="inlineStr">
+        <is>
+          <t>remote_api</t>
+        </is>
+      </c>
+      <c r="I80" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
       <c r="J80" t="inlineStr"/>
       <c r="K80" t="inlineStr"/>
       <c r="L80" t="inlineStr"/>
-      <c r="M80" t="inlineStr"/>
-      <c r="N80" t="inlineStr"/>
+      <c r="M80" t="inlineStr">
+        <is>
+          <t>Fetches the page, extracts title/description/key links</t>
+        </is>
+      </c>
+      <c r="N80" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="O80" t="inlineStr"/>
     </row>
     <row r="81">
@@ -4710,37 +4695,21 @@
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>write</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>affirmed</t>
-        </is>
-      </c>
-      <c r="H81" t="inlineStr">
-        <is>
-          <t>remote_api</t>
-        </is>
-      </c>
-      <c r="I81" t="inlineStr">
-        <is>
-          <t>tool</t>
-        </is>
-      </c>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H81" t="inlineStr"/>
+      <c r="I81" t="inlineStr"/>
       <c r="J81" t="inlineStr"/>
       <c r="K81" t="inlineStr"/>
       <c r="L81" t="inlineStr"/>
-      <c r="M81" t="inlineStr">
-        <is>
-          <t>Fetches the page, extracts title/description/key links</t>
-        </is>
-      </c>
-      <c r="N81" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="M81" t="inlineStr"/>
+      <c r="N81" t="inlineStr"/>
       <c r="O81" t="inlineStr"/>
     </row>
     <row r="82">
@@ -4769,7 +4738,7 @@
       </c>
       <c r="F82" t="inlineStr">
         <is>
-          <t>write</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G82" t="inlineStr">
@@ -4812,7 +4781,7 @@
       </c>
       <c r="F83" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>execute</t>
         </is>
       </c>
       <c r="G83" t="inlineStr">
@@ -4855,22 +4824,46 @@
       </c>
       <c r="F84" t="inlineStr">
         <is>
-          <t>execute</t>
+          <t>network</t>
         </is>
       </c>
       <c r="G84" t="inlineStr">
         <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H84" t="inlineStr"/>
-      <c r="I84" t="inlineStr"/>
+          <t>affirmed</t>
+        </is>
+      </c>
+      <c r="H84" t="inlineStr">
+        <is>
+          <t>remote_api</t>
+        </is>
+      </c>
+      <c r="I84" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
       <c r="J84" t="inlineStr"/>
       <c r="K84" t="inlineStr"/>
-      <c r="L84" t="inlineStr"/>
-      <c r="M84" t="inlineStr"/>
-      <c r="N84" t="inlineStr"/>
-      <c r="O84" t="inlineStr"/>
+      <c r="L84" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="M84" t="inlineStr">
+        <is>
+          <t>Fetches the page</t>
+        </is>
+      </c>
+      <c r="N84" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O84" t="inlineStr">
+        <is>
+          <t>N1: any URL</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -4878,87 +4871,20 @@
       </c>
       <c r="B85" t="inlineStr">
         <is>
-          <t>census_v2:54045</t>
+          <t>census_v2:25993</t>
         </is>
       </c>
       <c r="C85" t="inlineStr">
         <is>
-          <t>io.github.pipeworx-io/cftc-cot</t>
+          <t>io.github.Jorgeperez0825/v12-dfs</t>
         </is>
       </c>
       <c r="D85" t="inlineStr">
         <is>
-          <t>generate_llms_txt</t>
+          <t>admin_issue_key</t>
         </is>
       </c>
       <c r="E85" t="inlineStr">
-        <is>
-          <t>Generate a production-ready llms.txt file for any URL so AI crawlers (ChatGPT, Claude, Perplexity) can index the site cleanly. Fetches the page, extracts title/description/key links, and emits the standard llms.txt markdown format. Output is a single text blob ready to drop at site-root/llms.txt. Useful for: getting a client's site indexed by AI, drafting llms.txt for your own project, or auditing how an AI crawler would see a competitor.</t>
-        </is>
-      </c>
-      <c r="F85" t="inlineStr">
-        <is>
-          <t>network</t>
-        </is>
-      </c>
-      <c r="G85" t="inlineStr">
-        <is>
-          <t>affirmed</t>
-        </is>
-      </c>
-      <c r="H85" t="inlineStr">
-        <is>
-          <t>remote_api</t>
-        </is>
-      </c>
-      <c r="I85" t="inlineStr">
-        <is>
-          <t>tool</t>
-        </is>
-      </c>
-      <c r="J85" t="inlineStr"/>
-      <c r="K85" t="inlineStr"/>
-      <c r="L85" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
-      <c r="M85" t="inlineStr">
-        <is>
-          <t>Fetches the page</t>
-        </is>
-      </c>
-      <c r="N85" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="O85" t="inlineStr">
-        <is>
-          <t>N1: any URL</t>
-        </is>
-      </c>
-    </row>
-    <row r="86">
-      <c r="A86" t="n">
-        <v>85</v>
-      </c>
-      <c r="B86" t="inlineStr">
-        <is>
-          <t>census_v2:25993</t>
-        </is>
-      </c>
-      <c r="C86" t="inlineStr">
-        <is>
-          <t>io.github.Jorgeperez0825/v12-dfs</t>
-        </is>
-      </c>
-      <c r="D86" t="inlineStr">
-        <is>
-          <t>admin_issue_key</t>
-        </is>
-      </c>
-      <c r="E86" t="inlineStr">
         <is>
           <t>Issue Key
 Idempotently issue a user's API key and ALWAYS return the paste-able
@@ -4995,61 +4921,61 @@
 ```</t>
         </is>
       </c>
-      <c r="F86" t="inlineStr">
+      <c r="F85" t="inlineStr">
         <is>
           <t>read</t>
         </is>
       </c>
-      <c r="G86" t="inlineStr">
+      <c r="G85" t="inlineStr">
         <is>
           <t>affirmed</t>
         </is>
       </c>
-      <c r="H86" t="inlineStr">
+      <c r="H85" t="inlineStr">
         <is>
           <t>credentials</t>
         </is>
       </c>
-      <c r="I86" t="inlineStr">
+      <c r="I85" t="inlineStr">
         <is>
           <t>tool</t>
         </is>
       </c>
-      <c r="J86" t="inlineStr"/>
-      <c r="K86" t="inlineStr"/>
-      <c r="L86" t="inlineStr"/>
-      <c r="M86" t="inlineStr">
+      <c r="J85" t="inlineStr"/>
+      <c r="K85" t="inlineStr"/>
+      <c r="L85" t="inlineStr"/>
+      <c r="M85" t="inlineStr">
         <is>
           <t>Returns the email's existing active key</t>
         </is>
       </c>
-      <c r="N86" t="inlineStr">
+      <c r="N85" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="O86" t="inlineStr"/>
-    </row>
-    <row r="87">
-      <c r="A87" t="n">
-        <v>86</v>
-      </c>
-      <c r="B87" t="inlineStr">
+      <c r="O85" t="inlineStr"/>
+    </row>
+    <row r="86">
+      <c r="A86" t="n">
+        <v>85</v>
+      </c>
+      <c r="B86" t="inlineStr">
         <is>
           <t>census_v2:25993</t>
         </is>
       </c>
-      <c r="C87" t="inlineStr">
+      <c r="C86" t="inlineStr">
         <is>
           <t>io.github.Jorgeperez0825/v12-dfs</t>
         </is>
       </c>
-      <c r="D87" t="inlineStr">
+      <c r="D86" t="inlineStr">
         <is>
           <t>admin_issue_key</t>
         </is>
       </c>
-      <c r="E87" t="inlineStr">
+      <c r="E86" t="inlineStr">
         <is>
           <t>Issue Key
 Idempotently issue a user's API key and ALWAYS return the paste-able
@@ -5086,65 +5012,65 @@
 ```</t>
         </is>
       </c>
-      <c r="F87" t="inlineStr">
+      <c r="F86" t="inlineStr">
         <is>
           <t>write</t>
         </is>
       </c>
-      <c r="G87" t="inlineStr">
+      <c r="G86" t="inlineStr">
         <is>
           <t>affirmed</t>
         </is>
       </c>
-      <c r="H87" t="inlineStr">
+      <c r="H86" t="inlineStr">
         <is>
           <t>credentials</t>
         </is>
       </c>
-      <c r="I87" t="inlineStr">
+      <c r="I86" t="inlineStr">
         <is>
           <t>tool</t>
         </is>
       </c>
-      <c r="J87" t="inlineStr"/>
-      <c r="K87" t="inlineStr">
+      <c r="J86" t="inlineStr"/>
+      <c r="K86" t="inlineStr">
         <is>
           <t>additive</t>
         </is>
       </c>
-      <c r="L87" t="inlineStr"/>
-      <c r="M87" t="inlineStr">
+      <c r="L86" t="inlineStr"/>
+      <c r="M86" t="inlineStr">
         <is>
           <t>Idempotently issue a user's API key</t>
         </is>
       </c>
-      <c r="N87" t="inlineStr">
+      <c r="N86" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="O87" t="inlineStr"/>
-    </row>
-    <row r="88">
-      <c r="A88" t="n">
-        <v>87</v>
-      </c>
-      <c r="B88" t="inlineStr">
+      <c r="O86" t="inlineStr"/>
+    </row>
+    <row r="87">
+      <c r="A87" t="n">
+        <v>86</v>
+      </c>
+      <c r="B87" t="inlineStr">
         <is>
           <t>census_v2:25993</t>
         </is>
       </c>
-      <c r="C88" t="inlineStr">
+      <c r="C87" t="inlineStr">
         <is>
           <t>io.github.Jorgeperez0825/v12-dfs</t>
         </is>
       </c>
-      <c r="D88" t="inlineStr">
+      <c r="D87" t="inlineStr">
         <is>
           <t>admin_issue_key</t>
         </is>
       </c>
-      <c r="E88" t="inlineStr">
+      <c r="E87" t="inlineStr">
         <is>
           <t>Issue Key
 Idempotently issue a user's API key and ALWAYS return the paste-able
@@ -5181,70 +5107,70 @@
 ```</t>
         </is>
       </c>
-      <c r="F88" t="inlineStr">
+      <c r="F87" t="inlineStr">
         <is>
           <t>write</t>
         </is>
       </c>
-      <c r="G88" t="inlineStr">
+      <c r="G87" t="inlineStr">
         <is>
           <t>affirmed</t>
         </is>
       </c>
-      <c r="H88" t="inlineStr">
+      <c r="H87" t="inlineStr">
         <is>
           <t>credentials</t>
         </is>
       </c>
-      <c r="I88" t="inlineStr">
+      <c r="I87" t="inlineStr">
         <is>
           <t>tool</t>
         </is>
       </c>
-      <c r="J88" t="inlineStr">
+      <c r="J87" t="inlineStr">
         <is>
           <t>rotate=true</t>
         </is>
       </c>
-      <c r="K88" t="inlineStr">
+      <c r="K87" t="inlineStr">
         <is>
           <t>modifying</t>
         </is>
       </c>
-      <c r="L88" t="inlineStr"/>
-      <c r="M88" t="inlineStr">
+      <c r="L87" t="inlineStr"/>
+      <c r="M87" t="inlineStr">
         <is>
           <t>revokes
 the existing keys and mints a fresh one</t>
         </is>
       </c>
-      <c r="N88" t="inlineStr">
+      <c r="N87" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="O88" t="inlineStr"/>
-    </row>
-    <row r="89">
-      <c r="A89" t="n">
-        <v>88</v>
-      </c>
-      <c r="B89" t="inlineStr">
+      <c r="O87" t="inlineStr"/>
+    </row>
+    <row r="88">
+      <c r="A88" t="n">
+        <v>87</v>
+      </c>
+      <c r="B88" t="inlineStr">
         <is>
           <t>census_v2:25993</t>
         </is>
       </c>
-      <c r="C89" t="inlineStr">
+      <c r="C88" t="inlineStr">
         <is>
           <t>io.github.Jorgeperez0825/v12-dfs</t>
         </is>
       </c>
-      <c r="D89" t="inlineStr">
+      <c r="D88" t="inlineStr">
         <is>
           <t>admin_issue_key</t>
         </is>
       </c>
-      <c r="E89" t="inlineStr">
+      <c r="E88" t="inlineStr">
         <is>
           <t>Issue Key
 Idempotently issue a user's API key and ALWAYS return the paste-able
@@ -5281,70 +5207,70 @@
 ```</t>
         </is>
       </c>
-      <c r="F89" t="inlineStr">
+      <c r="F88" t="inlineStr">
         <is>
           <t>delete</t>
         </is>
       </c>
-      <c r="G89" t="inlineStr">
+      <c r="G88" t="inlineStr">
         <is>
           <t>uncertain</t>
         </is>
       </c>
-      <c r="H89" t="inlineStr">
+      <c r="H88" t="inlineStr">
         <is>
           <t>credentials</t>
         </is>
       </c>
-      <c r="I89" t="inlineStr">
+      <c r="I88" t="inlineStr">
         <is>
           <t>tool</t>
         </is>
       </c>
-      <c r="J89" t="inlineStr">
+      <c r="J88" t="inlineStr">
         <is>
           <t>rotate=true</t>
         </is>
       </c>
-      <c r="K89" t="inlineStr"/>
-      <c r="L89" t="inlineStr"/>
-      <c r="M89" t="inlineStr">
+      <c r="K88" t="inlineStr"/>
+      <c r="L88" t="inlineStr"/>
+      <c r="M88" t="inlineStr">
         <is>
           <t>revokes
 the existing keys</t>
         </is>
       </c>
-      <c r="N89" t="inlineStr">
+      <c r="N88" t="inlineStr">
         <is>
           <t>yes</t>
         </is>
       </c>
-      <c r="O89" t="inlineStr">
+      <c r="O88" t="inlineStr">
         <is>
           <t>open question: revocation as delete or modifying write</t>
         </is>
       </c>
     </row>
-    <row r="90">
-      <c r="A90" t="n">
-        <v>89</v>
-      </c>
-      <c r="B90" t="inlineStr">
+    <row r="89">
+      <c r="A89" t="n">
+        <v>88</v>
+      </c>
+      <c r="B89" t="inlineStr">
         <is>
           <t>census_v2:25993</t>
         </is>
       </c>
-      <c r="C90" t="inlineStr">
+      <c r="C89" t="inlineStr">
         <is>
           <t>io.github.Jorgeperez0825/v12-dfs</t>
         </is>
       </c>
-      <c r="D90" t="inlineStr">
+      <c r="D89" t="inlineStr">
         <is>
           <t>admin_issue_key</t>
         </is>
       </c>
-      <c r="E90" t="inlineStr">
+      <c r="E89" t="inlineStr">
         <is>
           <t>Issue Key
 Idempotently issue a user's API key and ALWAYS return the paste-able
@@ -5381,45 +5307,45 @@
 ```</t>
         </is>
       </c>
-      <c r="F90" t="inlineStr">
+      <c r="F89" t="inlineStr">
         <is>
           <t>execute</t>
         </is>
       </c>
-      <c r="G90" t="inlineStr">
-        <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H90" t="inlineStr"/>
-      <c r="I90" t="inlineStr"/>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="L90" t="inlineStr"/>
-      <c r="M90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
-      <c r="O90" t="inlineStr"/>
-    </row>
-    <row r="91">
-      <c r="A91" t="n">
-        <v>90</v>
-      </c>
-      <c r="B91" t="inlineStr">
+      <c r="G89" t="inlineStr">
+        <is>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H89" t="inlineStr"/>
+      <c r="I89" t="inlineStr"/>
+      <c r="J89" t="inlineStr"/>
+      <c r="K89" t="inlineStr"/>
+      <c r="L89" t="inlineStr"/>
+      <c r="M89" t="inlineStr"/>
+      <c r="N89" t="inlineStr"/>
+      <c r="O89" t="inlineStr"/>
+    </row>
+    <row r="90">
+      <c r="A90" t="n">
+        <v>89</v>
+      </c>
+      <c r="B90" t="inlineStr">
         <is>
           <t>census_v2:25993</t>
         </is>
       </c>
-      <c r="C91" t="inlineStr">
+      <c r="C90" t="inlineStr">
         <is>
           <t>io.github.Jorgeperez0825/v12-dfs</t>
         </is>
       </c>
-      <c r="D91" t="inlineStr">
+      <c r="D90" t="inlineStr">
         <is>
           <t>admin_issue_key</t>
         </is>
       </c>
-      <c r="E91" t="inlineStr">
+      <c r="E90" t="inlineStr">
         <is>
           <t>Issue Key
 Idempotently issue a user's API key and ALWAYS return the paste-able
@@ -5456,9 +5382,52 @@
 ```</t>
         </is>
       </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>network</t>
+        </is>
+      </c>
+      <c r="G90" t="inlineStr">
+        <is>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
+      <c r="J90" t="inlineStr"/>
+      <c r="K90" t="inlineStr"/>
+      <c r="L90" t="inlineStr"/>
+      <c r="M90" t="inlineStr"/>
+      <c r="N90" t="inlineStr"/>
+      <c r="O90" t="inlineStr"/>
+    </row>
+    <row r="91">
+      <c r="A91" t="n">
+        <v>90</v>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>census_v2:56462</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>io.github.pipeworx-io/country-state-city</t>
+        </is>
+      </c>
+      <c r="D91" t="inlineStr">
+        <is>
+          <t>remember</t>
+        </is>
+      </c>
+      <c r="E91" t="inlineStr">
+        <is>
+          <t>Save data the agent will need to reuse later — across this conversation or across sessions. Use when you discover something worth carrying forward (a resolved ticker, a target address, a user preference, a research subject) so you don't have to look it up again. Stored as a key-value pair scoped by your identifier. Authenticated users get persistent memory; anonymous sessions retain memory for 24 hours. Pair with recall to retrieve later, forget to delete.</t>
+        </is>
+      </c>
       <c r="F91" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>read</t>
         </is>
       </c>
       <c r="G91" t="inlineStr">
@@ -5501,22 +5470,46 @@
       </c>
       <c r="F92" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>write</t>
         </is>
       </c>
       <c r="G92" t="inlineStr">
         <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H92" t="inlineStr"/>
-      <c r="I92" t="inlineStr"/>
+          <t>affirmed</t>
+        </is>
+      </c>
+      <c r="H92" t="inlineStr">
+        <is>
+          <t>user_data</t>
+        </is>
+      </c>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
       <c r="J92" t="inlineStr"/>
-      <c r="K92" t="inlineStr"/>
+      <c r="K92" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="L92" t="inlineStr"/>
-      <c r="M92" t="inlineStr"/>
-      <c r="N92" t="inlineStr"/>
-      <c r="O92" t="inlineStr"/>
+      <c r="M92" t="inlineStr">
+        <is>
+          <t>Save data the agent will need to reuse later</t>
+        </is>
+      </c>
+      <c r="N92" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O92" t="inlineStr">
+        <is>
+          <t>key-value store: a reused key may overwrite</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -5544,7 +5537,7 @@
       </c>
       <c r="F93" t="inlineStr">
         <is>
-          <t>write</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G93" t="inlineStr">
@@ -5559,19 +5552,19 @@
       </c>
       <c r="I93" t="inlineStr">
         <is>
-          <t>tool</t>
-        </is>
-      </c>
-      <c r="J93" t="inlineStr"/>
-      <c r="K93" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+          <t>provider</t>
+        </is>
+      </c>
+      <c r="J93" t="inlineStr">
+        <is>
+          <t>anonymous session</t>
+        </is>
+      </c>
+      <c r="K93" t="inlineStr"/>
       <c r="L93" t="inlineStr"/>
       <c r="M93" t="inlineStr">
         <is>
-          <t>Save data the agent will need to reuse later</t>
+          <t>anonymous sessions retain memory for 24 hours</t>
         </is>
       </c>
       <c r="N93" t="inlineStr">
@@ -5581,7 +5574,7 @@
       </c>
       <c r="O93" t="inlineStr">
         <is>
-          <t>key-value store: a reused key may overwrite</t>
+          <t>A1: expiry by the service</t>
         </is>
       </c>
     </row>
@@ -5626,19 +5619,15 @@
       </c>
       <c r="I94" t="inlineStr">
         <is>
-          <t>provider</t>
-        </is>
-      </c>
-      <c r="J94" t="inlineStr">
-        <is>
-          <t>anonymous session</t>
-        </is>
-      </c>
+          <t>other_tool</t>
+        </is>
+      </c>
+      <c r="J94" t="inlineStr"/>
       <c r="K94" t="inlineStr"/>
       <c r="L94" t="inlineStr"/>
       <c r="M94" t="inlineStr">
         <is>
-          <t>anonymous sessions retain memory for 24 hours</t>
+          <t>forget to delete</t>
         </is>
       </c>
       <c r="N94" t="inlineStr">
@@ -5646,11 +5635,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="O94" t="inlineStr">
-        <is>
-          <t>A1: expiry by the service</t>
-        </is>
-      </c>
+      <c r="O94" t="inlineStr"/>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -5678,37 +5663,21 @@
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>execute</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>affirmed</t>
-        </is>
-      </c>
-      <c r="H95" t="inlineStr">
-        <is>
-          <t>user_data</t>
-        </is>
-      </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>other_tool</t>
-        </is>
-      </c>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H95" t="inlineStr"/>
+      <c r="I95" t="inlineStr"/>
       <c r="J95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr">
-        <is>
-          <t>forget to delete</t>
-        </is>
-      </c>
-      <c r="N95" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="M95" t="inlineStr"/>
+      <c r="N95" t="inlineStr"/>
       <c r="O95" t="inlineStr"/>
     </row>
     <row r="96">
@@ -5737,7 +5706,7 @@
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>execute</t>
+          <t>network</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
@@ -5760,41 +5729,57 @@
       </c>
       <c r="B97" t="inlineStr">
         <is>
-          <t>census_v2:56462</t>
+          <t>census_v2:52440</t>
         </is>
       </c>
       <c r="C97" t="inlineStr">
         <is>
-          <t>io.github.pipeworx-io/country-state-city</t>
+          <t>io.github.pipeworx-io/box</t>
         </is>
       </c>
       <c r="D97" t="inlineStr">
         <is>
-          <t>remember</t>
+          <t>resolution_diff</t>
         </is>
       </c>
       <c r="E97" t="inlineStr">
         <is>
-          <t>Save data the agent will need to reuse later — across this conversation or across sessions. Use when you discover something worth carrying forward (a resolved ticker, a target address, a user preference, a research subject) so you don't have to look it up again. Stored as a key-value pair scoped by your identifier. Authenticated users get persistent memory; anonymous sessions retain memory for 24 hours. Pair with recall to retrieve later, forget to delete.</t>
+          <t>Field-by-field diff of TWO markets' settlement clauses (one from each of `a` and `b`; either can be Polymarket or Kalshi) — runs resolution_audit on both sides and compares source, settle time, precision, and evidence standard. Returns `equivalent`: "true" only when both sides parsed with enough confidence to compare AND no field conflicts; "false" when a specific conflict was found (differing_fields names which — e.g. ["source","settle_time"] for a Polymarket Bitcoin market settling on Binance's 1-minute candle at noon ET versus a Kalshi KXBTCD market settling on CF Benchmarks' BRTI 60-second average at 5pm EDT — SAME asset, DIFFERENT contract); "unclear" when one or both sides could not be confidently parsed (an absence of evidence is not evidence of equivalence — read raw_clause yourself in that case). Only flags a field as differing when BOTH sides gave a SPECIFIC comparable answer — a named source (e.g. "Associated Press, Fox News, NBC") against a generic one (e.g. Kalshi's "consensus of media organizations") is treated as the same evidence standard, not a conflict, since that is standard election-market boilerplate on both venues. Use this before sizing a polymarket_kalshi_spread pair as a real cross-venue arb, or standalone to sanity-check any two markets you suspect settle on different things.</t>
         </is>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>read</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H97" t="inlineStr"/>
-      <c r="I97" t="inlineStr"/>
+          <t>affirmed</t>
+        </is>
+      </c>
+      <c r="H97" t="inlineStr">
+        <is>
+          <t>remote_api</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
       <c r="J97" t="inlineStr"/>
       <c r="K97" t="inlineStr"/>
       <c r="L97" t="inlineStr"/>
-      <c r="M97" t="inlineStr"/>
-      <c r="N97" t="inlineStr"/>
+      <c r="M97" t="inlineStr">
+        <is>
+          <t>runs resolution_audit on both sides and compares source, settle time, precision, and evidence standard</t>
+        </is>
+      </c>
+      <c r="N97" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="O97" t="inlineStr"/>
     </row>
     <row r="98">
@@ -5823,37 +5808,21 @@
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>write</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>affirmed</t>
-        </is>
-      </c>
-      <c r="H98" t="inlineStr">
-        <is>
-          <t>remote_api</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr">
-        <is>
-          <t>tool</t>
-        </is>
-      </c>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H98" t="inlineStr"/>
+      <c r="I98" t="inlineStr"/>
       <c r="J98" t="inlineStr"/>
       <c r="K98" t="inlineStr"/>
       <c r="L98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>runs resolution_audit on both sides and compares source, settle time, precision, and evidence standard</t>
-        </is>
-      </c>
-      <c r="N98" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="O98" t="inlineStr"/>
     </row>
     <row r="99">
@@ -5882,7 +5851,7 @@
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>write</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
@@ -5925,7 +5894,7 @@
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>execute</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
@@ -5968,7 +5937,7 @@
       </c>
       <c r="F101" t="inlineStr">
         <is>
-          <t>execute</t>
+          <t>network</t>
         </is>
       </c>
       <c r="G101" t="inlineStr">
@@ -5991,66 +5960,42 @@
       </c>
       <c r="B102" t="inlineStr">
         <is>
-          <t>census_v2:52440</t>
+          <t>census_v2:36107</t>
         </is>
       </c>
       <c r="C102" t="inlineStr">
         <is>
-          <t>io.github.pipeworx-io/box</t>
+          <t>io.github.getgapup/mcp-knowledge</t>
         </is>
       </c>
       <c r="D102" t="inlineStr">
         <is>
-          <t>resolution_diff</t>
+          <t>pentest_scope_estimator</t>
         </is>
       </c>
       <c r="E102" t="inlineStr">
         <is>
-          <t>Field-by-field diff of TWO markets' settlement clauses (one from each of `a` and `b`; either can be Polymarket or Kalshi) — runs resolution_audit on both sides and compares source, settle time, precision, and evidence standard. Returns `equivalent`: "true" only when both sides parsed with enough confidence to compare AND no field conflicts; "false" when a specific conflict was found (differing_fields names which — e.g. ["source","settle_time"] for a Polymarket Bitcoin market settling on Binance's 1-minute candle at noon ET versus a Kalshi KXBTCD market settling on CF Benchmarks' BRTI 60-second average at 5pm EDT — SAME asset, DIFFERENT contract); "unclear" when one or both sides could not be confidently parsed (an absence of evidence is not evidence of equivalence — read raw_clause yourself in that case). Only flags a field as differing when BOTH sides gave a SPECIFIC comparable answer — a named source (e.g. "Associated Press, Fox News, NBC") against a generic one (e.g. Kalshi's "consensus of media organizations") is treated as the same evidence standard, not a conflict, since that is standard election-market boilerplate on both venues. Use this before sizing a polymarket_kalshi_spread pair as a real cross-venue arb, or standalone to sanity-check any two markets you suspect settle on different things.</t>
+          <t>Estimateur de scope pentest — Gapup agent-payable C-suite expertise (RISK). Returns a structured, audited deliverable. Answers: For a &lt;scope_type&gt; pentest on &lt;tech_stack&gt; with &lt;N&gt; assets, what is the effort and cost estimate? · How much should I budget for a web application + API penetration test for SOC 2 Type II compliance? · What is the standard engagement plan (PTES phases + deliverables) for a &lt;scope_type&gt; pentest? · Which engagement type (black-box/grey-box/white-box/red-team) is recommended for my context? · What are the prerequisites and risks for a pentest engagement on my cloud infrastructure? Reference case: Acme SaaS Inc — Fintech B2B EU · web-app + API REST · 12 microservices Node.js AWS · . Inputs are validated server-side — send the documented case fields.</t>
         </is>
       </c>
       <c r="F102" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>read</t>
         </is>
       </c>
       <c r="G102" t="inlineStr">
         <is>
-          <t>uncertain</t>
-        </is>
-      </c>
-      <c r="H102" t="inlineStr">
-        <is>
-          <t>remote_api</t>
-        </is>
-      </c>
-      <c r="I102" t="inlineStr">
-        <is>
-          <t>tool</t>
-        </is>
-      </c>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H102" t="inlineStr"/>
+      <c r="I102" t="inlineStr"/>
       <c r="J102" t="inlineStr"/>
       <c r="K102" t="inlineStr"/>
-      <c r="L102" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="M102" t="inlineStr">
-        <is>
-          <t>either can be Polymarket or Kalshi</t>
-        </is>
-      </c>
-      <c r="N102" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="O102" t="inlineStr">
-        <is>
-          <t>market data from named venues; transport not stated</t>
-        </is>
-      </c>
+      <c r="L102" t="inlineStr"/>
+      <c r="M102" t="inlineStr"/>
+      <c r="N102" t="inlineStr"/>
+      <c r="O102" t="inlineStr"/>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -6078,7 +6023,7 @@
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>write</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
@@ -6121,7 +6066,7 @@
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>write</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
@@ -6164,7 +6109,7 @@
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>execute</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
@@ -6207,7 +6152,7 @@
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>execute</t>
+          <t>network</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
@@ -6230,41 +6175,57 @@
       </c>
       <c r="B107" t="inlineStr">
         <is>
-          <t>census_v2:36107</t>
+          <t>census_v2:69446</t>
         </is>
       </c>
       <c r="C107" t="inlineStr">
         <is>
-          <t>io.github.getgapup/mcp-knowledge</t>
+          <t>io.usefulapi/modern-treasury</t>
         </is>
       </c>
       <c r="D107" t="inlineStr">
         <is>
-          <t>pentest_scope_estimator</t>
+          <t>modern_treasury_list_expected_payments</t>
         </is>
       </c>
       <c r="E107" t="inlineStr">
         <is>
-          <t>Estimateur de scope pentest — Gapup agent-payable C-suite expertise (RISK). Returns a structured, audited deliverable. Answers: For a &lt;scope_type&gt; pentest on &lt;tech_stack&gt; with &lt;N&gt; assets, what is the effort and cost estimate? · How much should I budget for a web application + API penetration test for SOC 2 Type II compliance? · What is the standard engagement plan (PTES phases + deliverables) for a &lt;scope_type&gt; pentest? · Which engagement type (black-box/grey-box/white-box/red-team) is recommended for my context? · What are the prerequisites and risks for a pentest engagement on my cloud infrastructure? Reference case: Acme SaaS Inc — Fintech B2B EU · web-app + API REST · 12 microservices Node.js AWS · . Inputs are validated server-side — send the documented case fields.</t>
+          <t>List expected payments (READ ONLY). API: GET /expected_payments.</t>
         </is>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>read</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H107" t="inlineStr"/>
-      <c r="I107" t="inlineStr"/>
+          <t>affirmed</t>
+        </is>
+      </c>
+      <c r="H107" t="inlineStr">
+        <is>
+          <t>remote_api</t>
+        </is>
+      </c>
+      <c r="I107" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
       <c r="J107" t="inlineStr"/>
       <c r="K107" t="inlineStr"/>
       <c r="L107" t="inlineStr"/>
-      <c r="M107" t="inlineStr"/>
-      <c r="N107" t="inlineStr"/>
+      <c r="M107" t="inlineStr">
+        <is>
+          <t>List expected payments (READ ONLY).</t>
+        </is>
+      </c>
+      <c r="N107" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="O107" t="inlineStr"/>
     </row>
     <row r="108">
@@ -6293,17 +6254,17 @@
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>write</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>affirmed</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>remote_api</t>
+          <t>global</t>
         </is>
       </c>
       <c r="I108" t="inlineStr">
@@ -6316,7 +6277,7 @@
       <c r="L108" t="inlineStr"/>
       <c r="M108" t="inlineStr">
         <is>
-          <t>List expected payments (READ ONLY).</t>
+          <t>READ ONLY</t>
         </is>
       </c>
       <c r="N108" t="inlineStr">
@@ -6324,7 +6285,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="O108" t="inlineStr"/>
+      <c r="O108" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -6352,7 +6317,7 @@
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>write</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
@@ -6415,42 +6380,22 @@
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>execute</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>denied</t>
-        </is>
-      </c>
-      <c r="H110" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr">
-        <is>
-          <t>tool</t>
-        </is>
-      </c>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H110" t="inlineStr"/>
+      <c r="I110" t="inlineStr"/>
       <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>READ ONLY</t>
-        </is>
-      </c>
-      <c r="N110" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="O110" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
+      <c r="M110" t="inlineStr"/>
+      <c r="N110" t="inlineStr"/>
+      <c r="O110" t="inlineStr"/>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -6478,22 +6423,46 @@
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>execute</t>
+          <t>network</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H111" t="inlineStr"/>
-      <c r="I111" t="inlineStr"/>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="H111" t="inlineStr">
+        <is>
+          <t>remote_api</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
       <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
-      <c r="N111" t="inlineStr"/>
-      <c r="O111" t="inlineStr"/>
+      <c r="L111" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M111" t="inlineStr">
+        <is>
+          <t>API: GET /expected_payments</t>
+        </is>
+      </c>
+      <c r="N111" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O111" t="inlineStr">
+        <is>
+          <t>open question: relative API route without a host</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -6501,66 +6470,42 @@
       </c>
       <c r="B112" t="inlineStr">
         <is>
-          <t>census_v2:69446</t>
+          <t>census_v2:69614</t>
         </is>
       </c>
       <c r="C112" t="inlineStr">
         <is>
-          <t>io.usefulapi/modern-treasury</t>
+          <t>io.usefulapi/raisely</t>
         </is>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>modern_treasury_list_expected_payments</t>
+          <t>update_profile</t>
         </is>
       </c>
       <c r="E112" t="inlineStr">
         <is>
-          <t>List expected payments (READ ONLY). API: GET /expected_payments.</t>
+          <t>MUTATES Raisely data: updates a fundraising profile's goal/name/story. Raisely API: PATCH /profiles/{path} with the body wrapped as { data: {...} } (only included fields change). Use `fields` for goal, name, description/story, public, private, and any other documented field. Set overwriteCustomFields:true to overwrite (rather than preserve) unspecified custom fields. The path is never sent in the body.</t>
         </is>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>read</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>uncertain</t>
-        </is>
-      </c>
-      <c r="H112" t="inlineStr">
-        <is>
-          <t>remote_api</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>tool</t>
-        </is>
-      </c>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H112" t="inlineStr"/>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="M112" t="inlineStr">
-        <is>
-          <t>API: GET /expected_payments</t>
-        </is>
-      </c>
-      <c r="N112" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="O112" t="inlineStr">
-        <is>
-          <t>open question: relative API route without a host</t>
-        </is>
-      </c>
+      <c r="L112" t="inlineStr"/>
+      <c r="M112" t="inlineStr"/>
+      <c r="N112" t="inlineStr"/>
+      <c r="O112" t="inlineStr"/>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -6588,21 +6533,41 @@
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>write</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H113" t="inlineStr"/>
-      <c r="I113" t="inlineStr"/>
+          <t>affirmed</t>
+        </is>
+      </c>
+      <c r="H113" t="inlineStr">
+        <is>
+          <t>remote_api</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
       <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
+      <c r="K113" t="inlineStr">
+        <is>
+          <t>modifying</t>
+        </is>
+      </c>
       <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
+      <c r="M113" t="inlineStr">
+        <is>
+          <t>updates a fundraising profile's goal/name/story</t>
+        </is>
+      </c>
+      <c r="N113" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="O113" t="inlineStr"/>
     </row>
     <row r="114">
@@ -6649,16 +6614,20 @@
           <t>tool</t>
         </is>
       </c>
-      <c r="J114" t="inlineStr"/>
+      <c r="J114" t="inlineStr">
+        <is>
+          <t>overwriteCustomFields:true</t>
+        </is>
+      </c>
       <c r="K114" t="inlineStr">
         <is>
-          <t>modifying</t>
+          <t>overwrite</t>
         </is>
       </c>
       <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>updates a fundraising profile's goal/name/story</t>
+          <t>Set overwriteCustomFields:true to overwrite</t>
         </is>
       </c>
       <c r="N114" t="inlineStr">
@@ -6694,45 +6663,21 @@
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>write</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>affirmed</t>
-        </is>
-      </c>
-      <c r="H115" t="inlineStr">
-        <is>
-          <t>remote_api</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr">
-        <is>
-          <t>tool</t>
-        </is>
-      </c>
-      <c r="J115" t="inlineStr">
-        <is>
-          <t>overwriteCustomFields:true</t>
-        </is>
-      </c>
-      <c r="K115" t="inlineStr">
-        <is>
-          <t>overwrite</t>
-        </is>
-      </c>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H115" t="inlineStr"/>
+      <c r="I115" t="inlineStr"/>
+      <c r="J115" t="inlineStr"/>
+      <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>Set overwriteCustomFields:true to overwrite</t>
-        </is>
-      </c>
-      <c r="N115" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="M115" t="inlineStr"/>
+      <c r="N115" t="inlineStr"/>
       <c r="O115" t="inlineStr"/>
     </row>
     <row r="116">
@@ -6761,7 +6706,7 @@
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>execute</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
@@ -6804,22 +6749,46 @@
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>execute</t>
+          <t>network</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H117" t="inlineStr"/>
-      <c r="I117" t="inlineStr"/>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="H117" t="inlineStr">
+        <is>
+          <t>remote_api</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
       <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
-      <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr"/>
-      <c r="N117" t="inlineStr"/>
-      <c r="O117" t="inlineStr"/>
+      <c r="L117" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
+      <c r="M117" t="inlineStr">
+        <is>
+          <t>Raisely API: PATCH /profiles/{path}</t>
+        </is>
+      </c>
+      <c r="N117" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O117" t="inlineStr">
+        <is>
+          <t>N2 v2: method + route without a described call -&gt; uncertain</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -6827,27 +6796,27 @@
       </c>
       <c r="B118" t="inlineStr">
         <is>
-          <t>census_v2:69614</t>
+          <t>census_v2:35417</t>
         </is>
       </c>
       <c r="C118" t="inlineStr">
         <is>
-          <t>io.usefulapi/raisely</t>
+          <t>io.github.fxmacrodata/fxmacrodata</t>
         </is>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>update_profile</t>
+          <t>plot_visual_artifact</t>
         </is>
       </c>
       <c r="E118" t="inlineStr">
         <is>
-          <t>MUTATES Raisely data: updates a fundraising profile's goal/name/story. Raisely API: PATCH /profiles/{path} with the body wrapped as { data: {...} } (only included fields change). Use `fields` for goal, name, description/story, public, private, and any other documented field. Set overwriteCustomFields:true to overwrite (rather than preserve) unspecified custom fields. The path is never sent in the body.</t>
+          <t>Build a generic MCP Apps chart from one or more FXMacroData endpoint families: arbitrary plots, multi-series charts, and actual-vs-consensus views that combine announcements with predictions. Supported series sources are announcements, predictions, forex, commodities, and cot. For example, USD policy-rate midpoint actuals against market consensus use one announcements series for `usd/policy_rate_midpoint` and one predictions series for `usd/policy_rate_midpoint` with `prediction_class=forecaster_survey`. The tool does not fetch arbitrary URLs or run custom chart code; it only composes approved FXMacroData API surfaces into the comparison chart app. Access: USD is available without an API key; every other currency returns subscription_required with a subscribe link.</t>
         </is>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>read</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
@@ -6867,14 +6836,10 @@
       </c>
       <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+      <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>Raisely API: PATCH /profiles/{path}</t>
+          <t>Build a generic MCP Apps chart from one or more FXMacroData endpoint families</t>
         </is>
       </c>
       <c r="N118" t="inlineStr">
@@ -6884,7 +6849,7 @@
       </c>
       <c r="O118" t="inlineStr">
         <is>
-          <t>N2 v2: method + route without a described call -&gt; uncertain</t>
+          <t>RD: the description does not say whether the tool or the app fetches</t>
         </is>
       </c>
     </row>
@@ -6914,37 +6879,21 @@
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>write</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>affirmed</t>
-        </is>
-      </c>
-      <c r="H119" t="inlineStr">
-        <is>
-          <t>remote_api</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr">
-        <is>
-          <t>tool</t>
-        </is>
-      </c>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H119" t="inlineStr"/>
+      <c r="I119" t="inlineStr"/>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
       <c r="L119" t="inlineStr"/>
-      <c r="M119" t="inlineStr">
-        <is>
-          <t>Build a generic MCP Apps chart from one or more FXMacroData endpoint families</t>
-        </is>
-      </c>
-      <c r="N119" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="M119" t="inlineStr"/>
+      <c r="N119" t="inlineStr"/>
       <c r="O119" t="inlineStr"/>
     </row>
     <row r="120">
@@ -6973,7 +6922,7 @@
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>write</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
@@ -7016,21 +6965,37 @@
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>execute</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H121" t="inlineStr"/>
-      <c r="I121" t="inlineStr"/>
+          <t>denied</t>
+        </is>
+      </c>
+      <c r="H121" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="I121" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
       <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
-      <c r="M121" t="inlineStr"/>
-      <c r="N121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>or run custom chart code</t>
+        </is>
+      </c>
+      <c r="N121" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="O121" t="inlineStr"/>
     </row>
     <row r="122">
@@ -7059,7 +7024,7 @@
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>execute</t>
+          <t>network</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
@@ -7069,7 +7034,7 @@
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>other</t>
         </is>
       </c>
       <c r="I122" t="inlineStr">
@@ -7082,7 +7047,7 @@
       <c r="L122" t="inlineStr"/>
       <c r="M122" t="inlineStr">
         <is>
-          <t>or run custom chart code</t>
+          <t>The tool does not fetch arbitrary URLs</t>
         </is>
       </c>
       <c r="N122" t="inlineStr">
@@ -7090,7 +7055,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="O122" t="inlineStr"/>
+      <c r="O122" t="inlineStr">
+        <is>
+          <t>S1: arbitrary URLs only</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -7123,12 +7092,12 @@
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>denied</t>
+          <t>uncertain</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>remote_api</t>
         </is>
       </c>
       <c r="I123" t="inlineStr">
@@ -7138,10 +7107,14 @@
       </c>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
-      <c r="L123" t="inlineStr"/>
+      <c r="L123" t="inlineStr">
+        <is>
+          <t>closed</t>
+        </is>
+      </c>
       <c r="M123" t="inlineStr">
         <is>
-          <t>The tool does not fetch arbitrary URLs</t>
+          <t>it only composes approved FXMacroData API surfaces</t>
         </is>
       </c>
       <c r="N123" t="inlineStr">
@@ -7151,7 +7124,7 @@
       </c>
       <c r="O123" t="inlineStr">
         <is>
-          <t>S1: arbitrary URLs only</t>
+          <t>bounded to approved surfaces</t>
         </is>
       </c>
     </row>
@@ -7161,37 +7134,37 @@
       </c>
       <c r="B124" t="inlineStr">
         <is>
-          <t>census_v2:35417</t>
+          <t>census_v2:60950</t>
         </is>
       </c>
       <c r="C124" t="inlineStr">
         <is>
-          <t>io.github.fxmacrodata/fxmacrodata</t>
+          <t>io.github.realopengroup/mcp-server</t>
         </is>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>plot_visual_artifact</t>
+          <t>open_realopen</t>
         </is>
       </c>
       <c r="E124" t="inlineStr">
         <is>
-          <t>Build a generic MCP Apps chart from one or more FXMacroData endpoint families: arbitrary plots, multi-series charts, and actual-vs-consensus views that combine announcements with predictions. Supported series sources are announcements, predictions, forex, commodities, and cot. For example, USD policy-rate midpoint actuals against market consensus use one announcements series for `usd/policy_rate_midpoint` and one predictions series for `usd/policy_rate_midpoint` with `prediction_class=forecaster_survey`. The tool does not fetch arbitrary URLs or run custom chart code; it only composes approved FXMacroData API surfaces into the comparison chart app. Access: USD is available without an API key; every other currency returns subscription_required with a subscribe link.</t>
+          <t>Opens the RealOpen home, the full-screen app in the ChatGPT sidebar. Use it when the user asks to open RealOpen, open the RealOpen app or sidebar, or see an overview of where they stand. Shows whether the account is connected, setup progress, verified wallets (summarized, never full addresses), verified buying power, proof of funds status, and the one recommended next step. Read-only. Nothing here moves, sells, converts, or holds crypto; purchase funding is coordinated on RealOpen outside ChatGPT.</t>
         </is>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>read</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>uncertain</t>
+          <t>affirmed</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>remote_api</t>
+          <t>user_data</t>
         </is>
       </c>
       <c r="I124" t="inlineStr">
@@ -7201,14 +7174,10 @@
       </c>
       <c r="J124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
-      <c r="L124" t="inlineStr">
-        <is>
-          <t>closed</t>
-        </is>
-      </c>
+      <c r="L124" t="inlineStr"/>
       <c r="M124" t="inlineStr">
         <is>
-          <t>it only composes approved FXMacroData API surfaces</t>
+          <t>Shows whether the account is connected, setup progress, verified wallets</t>
         </is>
       </c>
       <c r="N124" t="inlineStr">
@@ -7216,11 +7185,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="O124" t="inlineStr">
-        <is>
-          <t>bounded to approved surfaces</t>
-        </is>
-      </c>
+      <c r="O124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -7248,17 +7213,17 @@
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>write</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>affirmed</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>user_data</t>
+          <t>global</t>
         </is>
       </c>
       <c r="I125" t="inlineStr">
@@ -7271,7 +7236,7 @@
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>Shows whether the account is connected, setup progress, verified wallets</t>
+          <t>Read-only.</t>
         </is>
       </c>
       <c r="N125" t="inlineStr">
@@ -7279,7 +7244,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="O125" t="inlineStr"/>
+      <c r="O125" t="inlineStr">
+        <is>
+          <t>B1</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -7307,7 +7276,7 @@
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>write</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
@@ -7370,42 +7339,22 @@
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>execute</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>denied</t>
-        </is>
-      </c>
-      <c r="H127" t="inlineStr">
-        <is>
-          <t>global</t>
-        </is>
-      </c>
-      <c r="I127" t="inlineStr">
-        <is>
-          <t>tool</t>
-        </is>
-      </c>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H127" t="inlineStr"/>
+      <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
-      <c r="M127" t="inlineStr">
-        <is>
-          <t>Read-only.</t>
-        </is>
-      </c>
-      <c r="N127" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="O127" t="inlineStr">
-        <is>
-          <t>B1</t>
-        </is>
-      </c>
+      <c r="M127" t="inlineStr"/>
+      <c r="N127" t="inlineStr"/>
+      <c r="O127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -7433,7 +7382,7 @@
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>execute</t>
+          <t>network</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
@@ -7456,27 +7405,27 @@
       </c>
       <c r="B129" t="inlineStr">
         <is>
-          <t>census_v2:60950</t>
+          <t>census_v2:71489</t>
         </is>
       </c>
       <c r="C129" t="inlineStr">
         <is>
-          <t>io.github.realopengroup/mcp-server</t>
+          <t>net.vibesprings/x402-tools</t>
         </is>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>open_realopen</t>
+          <t>register_watch</t>
         </is>
       </c>
       <c r="E129" t="inlineStr">
         <is>
-          <t>Opens the RealOpen home, the full-screen app in the ChatGPT sidebar. Use it when the user asks to open RealOpen, open the RealOpen app or sidebar, or see an overview of where they stand. Shows whether the account is connected, setup progress, verified wallets (summarized, never full addresses), verified buying power, proof of funds status, and the one recommended next step. Read-only. Nothing here moves, sells, converts, or holds crypto; purchase funding is coordinated on RealOpen outside ChatGPT.</t>
+          <t>Register a watch condition for real-time monitoring of prices, gas, weather, wallet balances/txs, or custom API endpoints. Returns watchId and checkEndpoint URL. [PAID: $0.01 USDC per call via x402 on Base. First call without payment_signature returns the payment requirements.]</t>
         </is>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>read</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
@@ -7519,21 +7468,41 @@
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>write</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H130" t="inlineStr"/>
-      <c r="I130" t="inlineStr"/>
+          <t>affirmed</t>
+        </is>
+      </c>
+      <c r="H130" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
       <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr"/>
+      <c r="K130" t="inlineStr">
+        <is>
+          <t>additive</t>
+        </is>
+      </c>
       <c r="L130" t="inlineStr"/>
-      <c r="M130" t="inlineStr"/>
-      <c r="N130" t="inlineStr"/>
+      <c r="M130" t="inlineStr">
+        <is>
+          <t>Register a watch condition</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="O130" t="inlineStr"/>
     </row>
     <row r="131">
@@ -7572,12 +7541,12 @@
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>database</t>
+          <t>other</t>
         </is>
       </c>
       <c r="I131" t="inlineStr">
         <is>
-          <t>tool</t>
+          <t>provider</t>
         </is>
       </c>
       <c r="J131" t="inlineStr"/>
@@ -7589,7 +7558,7 @@
       <c r="L131" t="inlineStr"/>
       <c r="M131" t="inlineStr">
         <is>
-          <t>Register a watch condition</t>
+          <t>$0.01 USDC per call via x402 on Base</t>
         </is>
       </c>
       <c r="N131" t="inlineStr">
@@ -7597,7 +7566,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="O131" t="inlineStr"/>
+      <c r="O131" t="inlineStr">
+        <is>
+          <t>payment</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -7625,46 +7598,22 @@
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>write</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>affirmed</t>
-        </is>
-      </c>
-      <c r="H132" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr">
-        <is>
-          <t>provider</t>
-        </is>
-      </c>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H132" t="inlineStr"/>
+      <c r="I132" t="inlineStr"/>
       <c r="J132" t="inlineStr"/>
-      <c r="K132" t="inlineStr">
-        <is>
-          <t>additive</t>
-        </is>
-      </c>
+      <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
-      <c r="M132" t="inlineStr">
-        <is>
-          <t>$0.01 USDC per call via x402 on Base</t>
-        </is>
-      </c>
-      <c r="N132" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="O132" t="inlineStr">
-        <is>
-          <t>payment</t>
-        </is>
-      </c>
+      <c r="M132" t="inlineStr"/>
+      <c r="N132" t="inlineStr"/>
+      <c r="O132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -7692,7 +7641,7 @@
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>execute</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
@@ -7735,22 +7684,46 @@
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>execute</t>
+          <t>network</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H134" t="inlineStr"/>
-      <c r="I134" t="inlineStr"/>
+          <t>affirmed</t>
+        </is>
+      </c>
+      <c r="H134" t="inlineStr">
+        <is>
+          <t>remote_api</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>provider</t>
+        </is>
+      </c>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
-      <c r="N134" t="inlineStr"/>
-      <c r="O134" t="inlineStr"/>
+      <c r="L134" t="inlineStr">
+        <is>
+          <t>open</t>
+        </is>
+      </c>
+      <c r="M134" t="inlineStr">
+        <is>
+          <t>real-time monitoring of prices, gas, weather, wallet balances/txs, or custom API endpoints</t>
+        </is>
+      </c>
+      <c r="N134" t="inlineStr">
+        <is>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O134" t="inlineStr">
+        <is>
+          <t>monitoring runs later on the service; custom endpoints = open</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -7758,27 +7731,28 @@
       </c>
       <c r="B135" t="inlineStr">
         <is>
-          <t>census_v2:71489</t>
+          <t>census_v2:2573</t>
         </is>
       </c>
       <c r="C135" t="inlineStr">
         <is>
-          <t>net.vibesprings/x402-tools</t>
+          <t>ai.oobeprotocol.sap.mcp/sap-mcp</t>
         </is>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>register_watch</t>
+          <t>sap_premium_validate_plugin_manifest</t>
         </is>
       </c>
       <c r="E135" t="inlineStr">
         <is>
-          <t>Register a watch condition for real-time monitoring of prices, gas, weather, wallet balances/txs, or custom API endpoints. Returns watchId and checkEndpoint URL. [PAID: $0.01 USDC per call via x402 on Base. First call without payment_signature returns the payment requirements.]</t>
+          <t>Free manifest validator for SAP MCP premium plugins. Validates ids, semver, descriptions, strict input/output schemas, x402/pay.sh pricing policies, and delivery contracts. It never executes plugin code or loads provider secrets.
+SAP MCP execution guidance: Intent: SAP MCP tool workflow. Pricing: free; call directly without x402. Routing: free hosted call; call directly and keep it small/exact when possible. Signer boundary: hosted reads/builders never receive keypair bytes; value-moving results must be finalized locally when signing is required.</t>
         </is>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>read</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
@@ -7788,34 +7762,30 @@
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>remote_api</t>
+          <t>other</t>
         </is>
       </c>
       <c r="I135" t="inlineStr">
         <is>
-          <t>provider</t>
+          <t>tool</t>
         </is>
       </c>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
-      <c r="L135" t="inlineStr">
-        <is>
-          <t>open</t>
-        </is>
-      </c>
+      <c r="L135" t="inlineStr"/>
       <c r="M135" t="inlineStr">
         <is>
-          <t>real-time monitoring of prices, gas, weather, wallet balances/txs, or custom API endpoints</t>
+          <t>Validates ids, semver, descriptions, strict input/output schemas</t>
         </is>
       </c>
       <c r="N135" t="inlineStr">
         <is>
-          <t>yes</t>
+          <t>no</t>
         </is>
       </c>
       <c r="O135" t="inlineStr">
         <is>
-          <t>monitoring runs later on the service; custom endpoints = open</t>
+          <t>other = the supplied manifest</t>
         </is>
       </c>
     </row>
@@ -7851,12 +7821,12 @@
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>affirmed</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>other</t>
+          <t>credentials</t>
         </is>
       </c>
       <c r="I136" t="inlineStr">
@@ -7869,7 +7839,7 @@
       <c r="L136" t="inlineStr"/>
       <c r="M136" t="inlineStr">
         <is>
-          <t>Validates ids, semver, descriptions, strict input/output schemas</t>
+          <t>or loads provider secrets</t>
         </is>
       </c>
       <c r="N136" t="inlineStr">
@@ -7877,11 +7847,7 @@
           <t>no</t>
         </is>
       </c>
-      <c r="O136" t="inlineStr">
-        <is>
-          <t>other = the supplied manifest</t>
-        </is>
-      </c>
+      <c r="O136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -7910,37 +7876,21 @@
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>write</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>denied</t>
-        </is>
-      </c>
-      <c r="H137" t="inlineStr">
-        <is>
-          <t>credentials</t>
-        </is>
-      </c>
-      <c r="I137" t="inlineStr">
-        <is>
-          <t>tool</t>
-        </is>
-      </c>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H137" t="inlineStr"/>
+      <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
       <c r="L137" t="inlineStr"/>
-      <c r="M137" t="inlineStr">
-        <is>
-          <t>or loads provider secrets</t>
-        </is>
-      </c>
-      <c r="N137" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="M137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="O137" t="inlineStr"/>
     </row>
     <row r="138">
@@ -7970,7 +7920,7 @@
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>write</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
@@ -8014,21 +7964,37 @@
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>execute</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H139" t="inlineStr"/>
-      <c r="I139" t="inlineStr"/>
+          <t>denied</t>
+        </is>
+      </c>
+      <c r="H139" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="I139" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
       <c r="L139" t="inlineStr"/>
-      <c r="M139" t="inlineStr"/>
-      <c r="N139" t="inlineStr"/>
+      <c r="M139" t="inlineStr">
+        <is>
+          <t>It never executes plugin code</t>
+        </is>
+      </c>
+      <c r="N139" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="O139" t="inlineStr"/>
     </row>
     <row r="140">
@@ -8058,37 +8024,21 @@
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>execute</t>
+          <t>network</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>denied</t>
-        </is>
-      </c>
-      <c r="H140" t="inlineStr">
-        <is>
-          <t>code</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>tool</t>
-        </is>
-      </c>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H140" t="inlineStr"/>
+      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
       <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>It never executes plugin code</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="M140" t="inlineStr"/>
+      <c r="N140" t="inlineStr"/>
       <c r="O140" t="inlineStr"/>
     </row>
     <row r="141">
@@ -8097,42 +8047,57 @@
       </c>
       <c r="B141" t="inlineStr">
         <is>
-          <t>census_v2:2573</t>
+          <t>census_v2:31007</t>
         </is>
       </c>
       <c r="C141" t="inlineStr">
         <is>
-          <t>ai.oobeprotocol.sap.mcp/sap-mcp</t>
+          <t>io.github.blackboxfoundry/livedatalink</t>
         </is>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>sap_premium_validate_plugin_manifest</t>
+          <t>fema_nfhl_get_inventory_item</t>
         </is>
       </c>
       <c r="E141" t="inlineStr">
         <is>
-          <t>Free manifest validator for SAP MCP premium plugins. Validates ids, semver, descriptions, strict input/output schemas, x402/pay.sh pricing policies, and delivery contracts. It never executes plugin code or loads provider secrets.
-SAP MCP execution guidance: Intent: SAP MCP tool workflow. Pricing: free; call directly without x402. Routing: free hosted call; call directly and keep it small/exact when possible. Signer boundary: hosted reads/builders never receive keypair bytes; value-moving results must be finalized locally when signing is required.</t>
+          <t>Get one self-hosted FEMA NFHL inventory unit by exact DFIRM ID. Returns jurisdiction, state, coverage-unit kind, package update date, advertised size, filename, canonical FEMA download URL, and immutable provenance. Use this to produce acquisition evidence after search. It does not fetch or inspect the geodatabase; use flood_zone_lookup for address/coordinate zone questions.</t>
         </is>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>read</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H141" t="inlineStr"/>
-      <c r="I141" t="inlineStr"/>
+          <t>affirmed</t>
+        </is>
+      </c>
+      <c r="H141" t="inlineStr">
+        <is>
+          <t>database</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
       <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr"/>
-      <c r="N141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>Get one self-hosted FEMA NFHL inventory unit by exact DFIRM ID.</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="O141" t="inlineStr"/>
     </row>
     <row r="142">
@@ -8166,12 +8131,12 @@
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>affirmed</t>
+          <t>denied</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>database</t>
+          <t>other</t>
         </is>
       </c>
       <c r="I142" t="inlineStr">
@@ -8184,7 +8149,7 @@
       <c r="L142" t="inlineStr"/>
       <c r="M142" t="inlineStr">
         <is>
-          <t>Get one self-hosted FEMA NFHL inventory unit by exact DFIRM ID.</t>
+          <t>It does not fetch or inspect the geodatabase</t>
         </is>
       </c>
       <c r="N142" t="inlineStr">
@@ -8192,7 +8157,11 @@
           <t>no</t>
         </is>
       </c>
-      <c r="O142" t="inlineStr"/>
+      <c r="O142" t="inlineStr">
+        <is>
+          <t>S1: the geodatabase only</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -8220,42 +8189,22 @@
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>write</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>denied</t>
-        </is>
-      </c>
-      <c r="H143" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr">
-        <is>
-          <t>tool</t>
-        </is>
-      </c>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr"/>
+      <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
       <c r="K143" t="inlineStr"/>
       <c r="L143" t="inlineStr"/>
-      <c r="M143" t="inlineStr">
-        <is>
-          <t>It does not fetch or inspect the geodatabase</t>
-        </is>
-      </c>
-      <c r="N143" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="O143" t="inlineStr">
-        <is>
-          <t>S1: the geodatabase only</t>
-        </is>
-      </c>
+      <c r="M143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
+      <c r="O143" t="inlineStr"/>
     </row>
     <row r="144">
       <c r="A144" t="n">
@@ -8283,7 +8232,7 @@
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>write</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
@@ -8326,7 +8275,7 @@
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>execute</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
@@ -8369,7 +8318,7 @@
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>execute</t>
+          <t>network</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
@@ -8392,42 +8341,62 @@
       </c>
       <c r="B147" t="inlineStr">
         <is>
-          <t>census_v2:31007</t>
+          <t>census_v2:59913</t>
         </is>
       </c>
       <c r="C147" t="inlineStr">
         <is>
-          <t>io.github.blackboxfoundry/livedatalink</t>
+          <t>io.github.pipeworx-io/data-oakland</t>
         </is>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>fema_nfhl_get_inventory_item</t>
+          <t>search_within</t>
         </is>
       </c>
       <c r="E147" t="inlineStr">
         <is>
-          <t>Get one self-hosted FEMA NFHL inventory unit by exact DFIRM ID. Returns jurisdiction, state, coverage-unit kind, package update date, advertised size, filename, canonical FEMA download URL, and immutable provenance. Use this to produce acquisition evidence after search. It does not fetch or inspect the geodatabase; use flood_zone_lookup for address/coordinate zone questions.</t>
+          <t>Semantic search INSIDE a fetched record. Pass the text you already pulled (e.g. a SEC 10-K body, an article, a long tool result) plus a natural-language query; get back the top-N passages with character offsets and similarity scores. Use when the record is too big to cram into the prompt — search_within saves context, returns only the passages that matter, and every passage carries an offset so the agent can verify a verbatim quote. Pairs with ask_pipeworx_grounded: fetch with the gateway, ground over the relevant passages instead of the whole document. BGE-base-en embeddings + cosine over 500-char overlapping windows; cap is 200K chars (longer inputs are truncated and flagged).</t>
         </is>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>read</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H147" t="inlineStr"/>
-      <c r="I147" t="inlineStr"/>
+          <t>affirmed</t>
+        </is>
+      </c>
+      <c r="H147" t="inlineStr">
+        <is>
+          <t>other</t>
+        </is>
+      </c>
+      <c r="I147" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
       <c r="J147" t="inlineStr"/>
       <c r="K147" t="inlineStr"/>
       <c r="L147" t="inlineStr"/>
-      <c r="M147" t="inlineStr"/>
-      <c r="N147" t="inlineStr"/>
-      <c r="O147" t="inlineStr"/>
+      <c r="M147" t="inlineStr">
+        <is>
+          <t>Semantic search INSIDE a fetched record.</t>
+        </is>
+      </c>
+      <c r="N147" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O147" t="inlineStr">
+        <is>
+          <t>other = text passed in</t>
+        </is>
+      </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
@@ -8455,42 +8424,22 @@
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>write</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>affirmed</t>
-        </is>
-      </c>
-      <c r="H148" t="inlineStr">
-        <is>
-          <t>other</t>
-        </is>
-      </c>
-      <c r="I148" t="inlineStr">
-        <is>
-          <t>tool</t>
-        </is>
-      </c>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H148" t="inlineStr"/>
+      <c r="I148" t="inlineStr"/>
       <c r="J148" t="inlineStr"/>
       <c r="K148" t="inlineStr"/>
       <c r="L148" t="inlineStr"/>
-      <c r="M148" t="inlineStr">
-        <is>
-          <t>Semantic search INSIDE a fetched record.</t>
-        </is>
-      </c>
-      <c r="N148" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="O148" t="inlineStr">
-        <is>
-          <t>other = text passed in</t>
-        </is>
-      </c>
+      <c r="M148" t="inlineStr"/>
+      <c r="N148" t="inlineStr"/>
+      <c r="O148" t="inlineStr"/>
     </row>
     <row r="149">
       <c r="A149" t="n">
@@ -8518,7 +8467,7 @@
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>write</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
@@ -8561,7 +8510,7 @@
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>execute</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
@@ -8604,7 +8553,7 @@
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>execute</t>
+          <t>network</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
@@ -8627,27 +8576,27 @@
       </c>
       <c r="B152" t="inlineStr">
         <is>
-          <t>census_v2:59913</t>
+          <t>census_v2:9322</t>
         </is>
       </c>
       <c r="C152" t="inlineStr">
         <is>
-          <t>io.github.pipeworx-io/data-oakland</t>
+          <t>com.babyblueviper/invinoveritas</t>
         </is>
       </c>
       <c r="D152" t="inlineStr">
         <is>
-          <t>search_within</t>
+          <t>execute</t>
         </is>
       </c>
       <c r="E152" t="inlineStr">
         <is>
-          <t>Semantic search INSIDE a fetched record. Pass the text you already pulled (e.g. a SEC 10-K body, an article, a long tool result) plus a natural-language query; get back the top-N passages with character offsets and similarity scores. Use when the record is too big to cram into the prompt — search_within saves context, returns only the passages that matter, and every passage carries an offset so the agent can verify a verbatim quote. Pairs with ask_pipeworx_grounded: fetch with the gateway, ground over the relevant passages instead of the whole document. BGE-base-en embeddings + cosine over 500-char overlapping windows; cap is 200K chars (longer inputs are truncated and flagged).</t>
+          <t>Paid secure Python execution that serious agents actually use. Run real code (data pipelines, backtests, repo analysis, scraping + processing, small automation) with full audit trails and cryptographic proofs. Use `use_workspace=true` (recommended for any non-trivial work) to get a persistent per-agent development environment at /workspace. Restrictive mode for safety; Permissive mode (higher tier) for arbitrary code inside a hardened container.</t>
         </is>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>read</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
@@ -8690,22 +8639,50 @@
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>write</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H153" t="inlineStr"/>
-      <c r="I153" t="inlineStr"/>
-      <c r="J153" t="inlineStr"/>
-      <c r="K153" t="inlineStr"/>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="H153" t="inlineStr">
+        <is>
+          <t>filesystem</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
+      <c r="J153" t="inlineStr">
+        <is>
+          <t>use_workspace=true</t>
+        </is>
+      </c>
+      <c r="K153" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
-      <c r="O153" t="inlineStr"/>
+      <c r="M153" t="inlineStr">
+        <is>
+          <t>get a persistent per-agent development environment at /workspace</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
+      <c r="O153" t="inlineStr">
+        <is>
+          <t>persistence alone does not establish a write</t>
+        </is>
+      </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
@@ -8733,50 +8710,22 @@
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>write</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>uncertain</t>
-        </is>
-      </c>
-      <c r="H154" t="inlineStr">
-        <is>
-          <t>filesystem</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>tool</t>
-        </is>
-      </c>
-      <c r="J154" t="inlineStr">
-        <is>
-          <t>use_workspace=true</t>
-        </is>
-      </c>
-      <c r="K154" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H154" t="inlineStr"/>
+      <c r="I154" t="inlineStr"/>
+      <c r="J154" t="inlineStr"/>
+      <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>get a persistent per-agent development environment at /workspace</t>
-        </is>
-      </c>
-      <c r="N154" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="O154" t="inlineStr">
-        <is>
-          <t>persistence alone does not establish a write</t>
-        </is>
-      </c>
+      <c r="M154" t="inlineStr"/>
+      <c r="N154" t="inlineStr"/>
+      <c r="O154" t="inlineStr"/>
     </row>
     <row r="155">
       <c r="A155" t="n">
@@ -8804,21 +8753,37 @@
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>execute</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H155" t="inlineStr"/>
-      <c r="I155" t="inlineStr"/>
+          <t>affirmed</t>
+        </is>
+      </c>
+      <c r="H155" t="inlineStr">
+        <is>
+          <t>code</t>
+        </is>
+      </c>
+      <c r="I155" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr"/>
-      <c r="N155" t="inlineStr"/>
+      <c r="M155" t="inlineStr">
+        <is>
+          <t>Run real code</t>
+        </is>
+      </c>
+      <c r="N155" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="O155" t="inlineStr"/>
     </row>
     <row r="156">
@@ -8847,17 +8812,17 @@
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>execute</t>
+          <t>network</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>affirmed</t>
+          <t>uncertain</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>code</t>
+          <t>remote_api</t>
         </is>
       </c>
       <c r="I156" t="inlineStr">
@@ -8867,18 +8832,26 @@
       </c>
       <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>unknown</t>
+        </is>
+      </c>
       <c r="M156" t="inlineStr">
         <is>
-          <t>Run real code</t>
+          <t>scraping + processing</t>
         </is>
       </c>
       <c r="N156" t="inlineStr">
         <is>
-          <t>no</t>
-        </is>
-      </c>
-      <c r="O156" t="inlineStr"/>
+          <t>yes</t>
+        </is>
+      </c>
+      <c r="O156" t="inlineStr">
+        <is>
+          <t>scraping implies network but the description does not say the sandbox has it</t>
+        </is>
+      </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
@@ -8886,66 +8859,42 @@
       </c>
       <c r="B157" t="inlineStr">
         <is>
-          <t>census_v2:9322</t>
+          <t>census_v2:42102</t>
         </is>
       </c>
       <c r="C157" t="inlineStr">
         <is>
-          <t>com.babyblueviper/invinoveritas</t>
+          <t>io.github.mcp-dir/portobank-mcp</t>
         </is>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>execute</t>
+          <t>openfinance_update_transaction_category</t>
         </is>
       </c>
       <c r="E157" t="inlineStr">
         <is>
-          <t>Paid secure Python execution that serious agents actually use. Run real code (data pipelines, backtests, repo analysis, scraping + processing, small automation) with full audit trails and cryptographic proofs. Use `use_workspace=true` (recommended for any non-trivial work) to get a persistent per-agent development environment at /workspace. Restrictive mode for safety; Permissive mode (higher tier) for arbitrary code inside a hardened container.</t>
+          <t>Corrects the category of one or more transactions (PATCH /transactions/:id). Pass `items` as an array of { transaction_id, category_id } — `transaction_id` comes from openfinance_list_transactions, `category_id` from openfinance_list_categories. This overrides Pluggy's automatic categorization AND teaches Pluggy: recategorizing a transaction automatically creates a Category Rule for this client (case-insensitive exact match on the transaction's data), so FUTURE similar transactions are categorized the same way — use this to fix miscategorized transactions and improve categorization accuracy going forward. Batch shape: returns `{ updated, results: [{ transaction_id, category, categoryId }], errors: [{ id, status, message }] }` — per-item errors do not fail the whole batch.</t>
         </is>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>network</t>
+          <t>read</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>uncertain</t>
-        </is>
-      </c>
-      <c r="H157" t="inlineStr">
-        <is>
-          <t>remote_api</t>
-        </is>
-      </c>
-      <c r="I157" t="inlineStr">
-        <is>
-          <t>tool</t>
-        </is>
-      </c>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H157" t="inlineStr"/>
+      <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr">
-        <is>
-          <t>unknown</t>
-        </is>
-      </c>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>scraping + processing</t>
-        </is>
-      </c>
-      <c r="N157" t="inlineStr">
-        <is>
-          <t>yes</t>
-        </is>
-      </c>
-      <c r="O157" t="inlineStr">
-        <is>
-          <t>scraping implies network but the description does not say the sandbox has it</t>
-        </is>
-      </c>
+      <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr"/>
+      <c r="N157" t="inlineStr"/>
+      <c r="O157" t="inlineStr"/>
     </row>
     <row r="158">
       <c r="A158" t="n">
@@ -8973,21 +8922,41 @@
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>read</t>
+          <t>write</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H158" t="inlineStr"/>
-      <c r="I158" t="inlineStr"/>
+          <t>affirmed</t>
+        </is>
+      </c>
+      <c r="H158" t="inlineStr">
+        <is>
+          <t>remote_api</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
       <c r="J158" t="inlineStr"/>
-      <c r="K158" t="inlineStr"/>
+      <c r="K158" t="inlineStr">
+        <is>
+          <t>modifying</t>
+        </is>
+      </c>
       <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr"/>
-      <c r="N158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>Corrects the category of one or more transactions (PATCH /transactions/:id)</t>
+        </is>
+      </c>
+      <c r="N158" t="inlineStr">
+        <is>
+          <t>no</t>
+        </is>
+      </c>
       <c r="O158" t="inlineStr"/>
     </row>
     <row r="159">
@@ -9037,13 +9006,13 @@
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr">
         <is>
-          <t>modifying</t>
+          <t>additive</t>
         </is>
       </c>
       <c r="L159" t="inlineStr"/>
       <c r="M159" t="inlineStr">
         <is>
-          <t>Corrects the category of one or more transactions (PATCH /transactions/:id)</t>
+          <t>recategorizing a transaction automatically creates a Category Rule for this client</t>
         </is>
       </c>
       <c r="N159" t="inlineStr">
@@ -9079,41 +9048,21 @@
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>write</t>
+          <t>delete</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>affirmed</t>
-        </is>
-      </c>
-      <c r="H160" t="inlineStr">
-        <is>
-          <t>remote_api</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>tool</t>
-        </is>
-      </c>
+          <t>not_stated</t>
+        </is>
+      </c>
+      <c r="H160" t="inlineStr"/>
+      <c r="I160" t="inlineStr"/>
       <c r="J160" t="inlineStr"/>
-      <c r="K160" t="inlineStr">
-        <is>
-          <t>additive</t>
-        </is>
-      </c>
+      <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr"/>
-      <c r="M160" t="inlineStr">
-        <is>
-          <t>recategorizing a transaction automatically creates a Category Rule for this client</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr">
-        <is>
-          <t>no</t>
-        </is>
-      </c>
+      <c r="M160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
       <c r="O160" t="inlineStr"/>
     </row>
     <row r="161">
@@ -9142,7 +9091,7 @@
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>delete</t>
+          <t>execute</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
@@ -9185,85 +9134,42 @@
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>execute</t>
+          <t>network</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>not_stated</t>
-        </is>
-      </c>
-      <c r="H162" t="inlineStr"/>
-      <c r="I162" t="inlineStr"/>
+          <t>uncertain</t>
+        </is>
+      </c>
+      <c r="H162" t="inlineStr">
+        <is>
+          <t>remote_api</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>tool</t>
+        </is>
+      </c>
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
-      <c r="L162" t="inlineStr"/>
-      <c r="M162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
-      <c r="O162" t="inlineStr"/>
-    </row>
-    <row r="163">
-      <c r="A163" t="n">
-        <v>162</v>
-      </c>
-      <c r="B163" t="inlineStr">
-        <is>
-          <t>census_v2:42102</t>
-        </is>
-      </c>
-      <c r="C163" t="inlineStr">
-        <is>
-          <t>io.github.mcp-dir/portobank-mcp</t>
-        </is>
-      </c>
-      <c r="D163" t="inlineStr">
-        <is>
-          <t>openfinance_update_transaction_category</t>
-        </is>
-      </c>
-      <c r="E163" t="inlineStr">
-        <is>
-          <t>Corrects the category of one or more transactions (PATCH /transactions/:id). Pass `items` as an array of { transaction_id, category_id } — `transaction_id` comes from openfinance_list_transactions, `category_id` from openfinance_list_categories. This overrides Pluggy's automatic categorization AND teaches Pluggy: recategorizing a transaction automatically creates a Category Rule for this client (case-insensitive exact match on the transaction's data), so FUTURE similar transactions are categorized the same way — use this to fix miscategorized transactions and improve categorization accuracy going forward. Batch shape: returns `{ updated, results: [{ transaction_id, category, categoryId }], errors: [{ id, status, message }] }` — per-item errors do not fail the whole batch.</t>
-        </is>
-      </c>
-      <c r="F163" t="inlineStr">
-        <is>
-          <t>network</t>
-        </is>
-      </c>
-      <c r="G163" t="inlineStr">
-        <is>
-          <t>uncertain</t>
-        </is>
-      </c>
-      <c r="H163" t="inlineStr">
-        <is>
-          <t>remote_api</t>
-        </is>
-      </c>
-      <c r="I163" t="inlineStr">
-        <is>
-          <t>tool</t>
-        </is>
-      </c>
-      <c r="J163" t="inlineStr"/>
-      <c r="K163" t="inlineStr"/>
-      <c r="L163" t="inlineStr">
+      <c r="L162" t="inlineStr">
         <is>
           <t>unknown</t>
         </is>
       </c>
-      <c r="M163" t="inlineStr">
+      <c r="M162" t="inlineStr">
         <is>
           <t>This overrides Pluggy's automatic categorization</t>
         </is>
       </c>
-      <c r="N163" t="inlineStr">
+      <c r="N162" t="inlineStr">
         <is>
           <t>no</t>
         </is>
       </c>
-      <c r="O163" t="inlineStr">
+      <c r="O162" t="inlineStr">
         <is>
           <t>names the Pluggy service; transport not stated</t>
         </is>
